--- a/research/traditional_assets/database/data/austria/austria_steel.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_steel.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09353952157583045</v>
+        <v>0.09334922672404845</v>
       </c>
       <c r="C2">
-        <v>5845.665492292472</v>
+        <v>5798.24600021779</v>
       </c>
       <c r="D2">
-        <v>5459.565492292471</v>
+        <v>5481.41500021779</v>
       </c>
       <c r="E2">
-        <v>-3673.3</v>
+        <v>-3604.031</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69.26899999999999</v>
       </c>
       <c r="G2">
         <v>386.1</v>
@@ -1457,28 +1457,28 @@
         <v>1114.375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.484230699999999</v>
       </c>
       <c r="N2">
-        <v>1114.375</v>
+        <v>1110.8907693</v>
       </c>
       <c r="O2">
-        <v>267.4499999999999</v>
+        <v>266.613784632</v>
       </c>
       <c r="P2">
-        <v>846.9249999999998</v>
+        <v>844.2769846679998</v>
       </c>
       <c r="Q2">
-        <v>1600.425</v>
+        <v>1597.776984668</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09353952157583045</v>
+        <v>0.09390600679196814</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9891101320923001</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>319.8338732277401</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09334922672404845</v>
+        <v>0.09315893187226647</v>
       </c>
       <c r="C3">
-        <v>5798.24600021779</v>
+        <v>5751.002096937357</v>
       </c>
       <c r="D3">
-        <v>5481.41500021779</v>
+        <v>5503.440096937356</v>
       </c>
       <c r="E3">
-        <v>-3604.031</v>
+        <v>-3534.762</v>
       </c>
       <c r="F3">
-        <v>69.26899999999999</v>
+        <v>138.538</v>
       </c>
       <c r="G3">
         <v>386.1</v>
@@ -1539,28 +1539,28 @@
         <v>1114.375</v>
       </c>
       <c r="M3">
-        <v>3.484230699999999</v>
+        <v>6.968461399999999</v>
       </c>
       <c r="N3">
-        <v>1110.8907693</v>
+        <v>1107.4065386</v>
       </c>
       <c r="O3">
-        <v>266.613784632</v>
+        <v>265.7775692639999</v>
       </c>
       <c r="P3">
-        <v>844.2769846679998</v>
+        <v>841.6289693359998</v>
       </c>
       <c r="Q3">
-        <v>1597.776984668</v>
+        <v>1595.128969336</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09390600679196814</v>
+        <v>0.0942799712982311</v>
       </c>
       <c r="T3">
-        <v>0.9891101320923001</v>
+        <v>0.9967992359455289</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>319.8338732277401</v>
+        <v>159.91693661387</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09315893187226647</v>
+        <v>0.09296863702048448</v>
       </c>
       <c r="C4">
-        <v>5751.002096937357</v>
+        <v>5703.935907611809</v>
       </c>
       <c r="D4">
-        <v>5503.440096937356</v>
+        <v>5525.642907611808</v>
       </c>
       <c r="E4">
-        <v>-3534.762</v>
+        <v>-3465.493</v>
       </c>
       <c r="F4">
-        <v>138.538</v>
+        <v>207.807</v>
       </c>
       <c r="G4">
         <v>386.1</v>
@@ -1621,28 +1621,28 @@
         <v>1114.375</v>
       </c>
       <c r="M4">
-        <v>6.968461399999999</v>
+        <v>10.4526921</v>
       </c>
       <c r="N4">
-        <v>1107.4065386</v>
+        <v>1103.9223079</v>
       </c>
       <c r="O4">
-        <v>265.7775692639999</v>
+        <v>264.941353896</v>
       </c>
       <c r="P4">
-        <v>841.6289693359998</v>
+        <v>838.9809540039998</v>
       </c>
       <c r="Q4">
-        <v>1595.128969336</v>
+        <v>1592.480954004</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0942799712982311</v>
+        <v>0.0946616464128706</v>
       </c>
       <c r="T4">
-        <v>0.9967992359455289</v>
+        <v>1.004646878022536</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>159.91693661387</v>
+        <v>106.6112910759134</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09296863702048448</v>
+        <v>0.09277834216870248</v>
       </c>
       <c r="C5">
-        <v>5703.935907611809</v>
+        <v>5657.049591835279</v>
       </c>
       <c r="D5">
-        <v>5525.642907611808</v>
+        <v>5548.025591835279</v>
       </c>
       <c r="E5">
-        <v>-3465.493</v>
+        <v>-3396.224</v>
       </c>
       <c r="F5">
-        <v>207.807</v>
+        <v>277.076</v>
       </c>
       <c r="G5">
         <v>386.1</v>
@@ -1703,28 +1703,28 @@
         <v>1114.375</v>
       </c>
       <c r="M5">
-        <v>10.4526921</v>
+        <v>13.9369228</v>
       </c>
       <c r="N5">
-        <v>1103.9223079</v>
+        <v>1100.4380772</v>
       </c>
       <c r="O5">
-        <v>264.941353896</v>
+        <v>264.1051385279999</v>
       </c>
       <c r="P5">
-        <v>838.9809540039998</v>
+        <v>836.3329386719997</v>
       </c>
       <c r="Q5">
-        <v>1592.480954004</v>
+        <v>1589.832938672</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0946616464128706</v>
+        <v>0.09505127309239843</v>
       </c>
       <c r="T5">
-        <v>1.004646878022536</v>
+        <v>1.012658012642814</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>106.6112910759134</v>
+        <v>79.958468306935</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09277834216870248</v>
+        <v>0.09258804731692048</v>
       </c>
       <c r="C6">
-        <v>5657.049591835279</v>
+        <v>5610.34534433563</v>
       </c>
       <c r="D6">
-        <v>5548.025591835279</v>
+        <v>5570.59034433563</v>
       </c>
       <c r="E6">
-        <v>-3396.224</v>
+        <v>-3326.955</v>
       </c>
       <c r="F6">
-        <v>277.076</v>
+        <v>346.345</v>
       </c>
       <c r="G6">
         <v>386.1</v>
@@ -1785,28 +1785,28 @@
         <v>1114.375</v>
       </c>
       <c r="M6">
-        <v>13.9369228</v>
+        <v>17.4211535</v>
       </c>
       <c r="N6">
-        <v>1100.4380772</v>
+        <v>1096.9538465</v>
       </c>
       <c r="O6">
-        <v>264.1051385279999</v>
+        <v>263.2689231599999</v>
       </c>
       <c r="P6">
-        <v>836.3329386719997</v>
+        <v>833.6849233399998</v>
       </c>
       <c r="Q6">
-        <v>1589.832938672</v>
+        <v>1587.18492334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09505127309239843</v>
+        <v>0.09544910243886368</v>
       </c>
       <c r="T6">
-        <v>1.012658012642814</v>
+        <v>1.020837802728781</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.958468306935</v>
+        <v>63.96677464554801</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09258804731692048</v>
+        <v>0.09239775246513852</v>
       </c>
       <c r="C7">
-        <v>5610.34534433563</v>
+        <v>5563.82539569184</v>
       </c>
       <c r="D7">
-        <v>5570.59034433563</v>
+        <v>5593.339395691839</v>
       </c>
       <c r="E7">
-        <v>-3326.955</v>
+        <v>-3257.686</v>
       </c>
       <c r="F7">
-        <v>346.345</v>
+        <v>415.614</v>
       </c>
       <c r="G7">
         <v>386.1</v>
@@ -1867,28 +1867,28 @@
         <v>1114.375</v>
       </c>
       <c r="M7">
-        <v>17.4211535</v>
+        <v>20.9053842</v>
       </c>
       <c r="N7">
-        <v>1096.9538465</v>
+        <v>1093.4696158</v>
       </c>
       <c r="O7">
-        <v>263.2689231599999</v>
+        <v>262.4327077919999</v>
       </c>
       <c r="P7">
-        <v>833.6849233399998</v>
+        <v>831.0369080079997</v>
       </c>
       <c r="Q7">
-        <v>1587.18492334</v>
+        <v>1584.536908008</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09544910243886368</v>
+        <v>0.09585539623950906</v>
       </c>
       <c r="T7">
-        <v>1.020837802728781</v>
+        <v>1.029191630901685</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.96677464554801</v>
+        <v>53.30564553795666</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09239775246513852</v>
+        <v>0.09220745761335651</v>
       </c>
       <c r="C8">
-        <v>5563.82539569184</v>
+        <v>5517.492013069063</v>
       </c>
       <c r="D8">
-        <v>5593.339395691839</v>
+        <v>5616.275013069063</v>
       </c>
       <c r="E8">
-        <v>-3257.686</v>
+        <v>-3188.417</v>
       </c>
       <c r="F8">
-        <v>415.614</v>
+        <v>484.8829999999999</v>
       </c>
       <c r="G8">
         <v>386.1</v>
@@ -1949,28 +1949,28 @@
         <v>1114.375</v>
       </c>
       <c r="M8">
-        <v>20.9053842</v>
+        <v>24.38961489999999</v>
       </c>
       <c r="N8">
-        <v>1093.4696158</v>
+        <v>1089.9853851</v>
       </c>
       <c r="O8">
-        <v>262.4327077919999</v>
+        <v>261.596492424</v>
       </c>
       <c r="P8">
-        <v>831.0369080079997</v>
+        <v>828.3888926759998</v>
       </c>
       <c r="Q8">
-        <v>1584.536908008</v>
+        <v>1581.888892676</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09585539623950906</v>
+        <v>0.09627042754124356</v>
       </c>
       <c r="T8">
-        <v>1.029191630901685</v>
+        <v>1.03772511129336</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.30564553795667</v>
+        <v>45.69055331824858</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09220745761335651</v>
+        <v>0.09201716276157451</v>
       </c>
       <c r="C9">
-        <v>5517.492013069063</v>
+        <v>5471.347500971802</v>
       </c>
       <c r="D9">
-        <v>5616.275013069063</v>
+        <v>5639.399500971802</v>
       </c>
       <c r="E9">
-        <v>-3188.417</v>
+        <v>-3119.148</v>
       </c>
       <c r="F9">
-        <v>484.883</v>
+        <v>554.1519999999999</v>
       </c>
       <c r="G9">
         <v>386.1</v>
@@ -2031,28 +2031,28 @@
         <v>1114.375</v>
       </c>
       <c r="M9">
-        <v>24.3896149</v>
+        <v>27.8738456</v>
       </c>
       <c r="N9">
-        <v>1089.9853851</v>
+        <v>1086.5011544</v>
       </c>
       <c r="O9">
-        <v>261.596492424</v>
+        <v>260.7602770559999</v>
       </c>
       <c r="P9">
-        <v>828.3888926759998</v>
+        <v>825.7408773439997</v>
       </c>
       <c r="Q9">
-        <v>1581.888892676</v>
+        <v>1579.240877344</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09627042754124356</v>
+        <v>0.09669448126258098</v>
       </c>
       <c r="T9">
-        <v>1.03772511129336</v>
+        <v>1.046444102128332</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.69055331824857</v>
+        <v>39.9792341534675</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09201716276157451</v>
+        <v>0.09182686790979253</v>
       </c>
       <c r="C10">
-        <v>5471.347500971802</v>
+        <v>5425.394202015811</v>
       </c>
       <c r="D10">
-        <v>5639.399500971802</v>
+        <v>5662.715202015811</v>
       </c>
       <c r="E10">
-        <v>-3119.148</v>
+        <v>-3049.879</v>
       </c>
       <c r="F10">
-        <v>554.1519999999999</v>
+        <v>623.4209999999999</v>
       </c>
       <c r="G10">
         <v>386.1</v>
@@ -2113,28 +2113,28 @@
         <v>1114.375</v>
       </c>
       <c r="M10">
-        <v>27.8738456</v>
+        <v>31.3580763</v>
       </c>
       <c r="N10">
-        <v>1086.5011544</v>
+        <v>1083.0169237</v>
       </c>
       <c r="O10">
-        <v>260.7602770559999</v>
+        <v>259.9240616879999</v>
       </c>
       <c r="P10">
-        <v>825.7408773439997</v>
+        <v>823.0928620119998</v>
       </c>
       <c r="Q10">
-        <v>1579.240877344</v>
+        <v>1576.592862012</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09669448126258098</v>
+        <v>0.09712785484592584</v>
       </c>
       <c r="T10">
-        <v>1.046444102128332</v>
+        <v>1.055354719135502</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.9792341534675</v>
+        <v>35.53709702530445</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09182686790979253</v>
+        <v>0.09163657305801054</v>
       </c>
       <c r="C11">
-        <v>5425.394202015811</v>
+        <v>5379.63449771921</v>
       </c>
       <c r="D11">
-        <v>5662.715202015811</v>
+        <v>5686.224497719209</v>
       </c>
       <c r="E11">
-        <v>-3049.879</v>
+        <v>-2980.61</v>
       </c>
       <c r="F11">
-        <v>623.4209999999999</v>
+        <v>692.6899999999999</v>
       </c>
       <c r="G11">
         <v>386.1</v>
@@ -2195,28 +2195,28 @@
         <v>1114.375</v>
       </c>
       <c r="M11">
-        <v>31.3580763</v>
+        <v>34.842307</v>
       </c>
       <c r="N11">
-        <v>1083.0169237</v>
+        <v>1079.532693</v>
       </c>
       <c r="O11">
-        <v>259.9240616879999</v>
+        <v>259.08784632</v>
       </c>
       <c r="P11">
-        <v>823.0928620119998</v>
+        <v>820.44484668</v>
       </c>
       <c r="Q11">
-        <v>1576.592862012</v>
+        <v>1573.94484668</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09712785484592584</v>
+        <v>0.09757085895334504</v>
       </c>
       <c r="T11">
-        <v>1.055354719135502</v>
+        <v>1.064463349853943</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.53709702530445</v>
+        <v>31.983387322774</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09163657305801054</v>
+        <v>0.09144627820622854</v>
       </c>
       <c r="C12">
-        <v>5379.634497719209</v>
+        <v>5334.070809313376</v>
       </c>
       <c r="D12">
-        <v>5686.224497719209</v>
+        <v>5709.929809313376</v>
       </c>
       <c r="E12">
-        <v>-2980.61</v>
+        <v>-2911.341</v>
       </c>
       <c r="F12">
-        <v>692.6900000000001</v>
+        <v>761.9589999999999</v>
       </c>
       <c r="G12">
         <v>386.1</v>
@@ -2277,28 +2277,28 @@
         <v>1114.375</v>
       </c>
       <c r="M12">
-        <v>34.842307</v>
+        <v>38.3265377</v>
       </c>
       <c r="N12">
-        <v>1079.532693</v>
+        <v>1076.0484623</v>
       </c>
       <c r="O12">
-        <v>259.08784632</v>
+        <v>258.2516309519999</v>
       </c>
       <c r="P12">
-        <v>820.44484668</v>
+        <v>817.7968313479998</v>
       </c>
       <c r="Q12">
-        <v>1573.94484668</v>
+        <v>1571.296831348</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09757085895334504</v>
+        <v>0.09802381820924555</v>
       </c>
       <c r="T12">
-        <v>1.064463349853943</v>
+        <v>1.073776668903135</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.983387322774</v>
+        <v>29.07580665706728</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09144627820622854</v>
+        <v>0.09125598335444654</v>
       </c>
       <c r="C13">
-        <v>5334.070809313376</v>
+        <v>5288.705598574215</v>
       </c>
       <c r="D13">
-        <v>5709.929809313376</v>
+        <v>5733.833598574215</v>
       </c>
       <c r="E13">
-        <v>-2911.341</v>
+        <v>-2842.072</v>
       </c>
       <c r="F13">
-        <v>761.9589999999999</v>
+        <v>831.228</v>
       </c>
       <c r="G13">
         <v>386.1</v>
@@ -2359,28 +2359,28 @@
         <v>1114.375</v>
       </c>
       <c r="M13">
-        <v>38.3265377</v>
+        <v>41.81076839999999</v>
       </c>
       <c r="N13">
-        <v>1076.0484623</v>
+        <v>1072.5642316</v>
       </c>
       <c r="O13">
-        <v>258.2516309519999</v>
+        <v>257.415415584</v>
       </c>
       <c r="P13">
-        <v>817.7968313479998</v>
+        <v>815.148816016</v>
       </c>
       <c r="Q13">
-        <v>1571.296831348</v>
+        <v>1568.648816016</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09802381820924555</v>
+        <v>0.09848707199368925</v>
       </c>
       <c r="T13">
-        <v>1.073776668903135</v>
+        <v>1.083301654294353</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.07580665706728</v>
+        <v>26.65282276897834</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09125598335444654</v>
+        <v>0.09106568850266455</v>
       </c>
       <c r="C14">
-        <v>5288.705598574215</v>
+        <v>5243.541368674399</v>
       </c>
       <c r="D14">
-        <v>5733.833598574215</v>
+        <v>5757.938368674399</v>
       </c>
       <c r="E14">
-        <v>-2842.072</v>
+        <v>-2772.803</v>
       </c>
       <c r="F14">
-        <v>831.228</v>
+        <v>900.497</v>
       </c>
       <c r="G14">
         <v>386.1</v>
@@ -2441,28 +2441,28 @@
         <v>1114.375</v>
       </c>
       <c r="M14">
-        <v>41.81076839999999</v>
+        <v>45.2949991</v>
       </c>
       <c r="N14">
-        <v>1072.5642316</v>
+        <v>1069.0800009</v>
       </c>
       <c r="O14">
-        <v>257.415415584</v>
+        <v>256.5792002159999</v>
       </c>
       <c r="P14">
-        <v>815.148816016</v>
+        <v>812.5008006839998</v>
       </c>
       <c r="Q14">
-        <v>1568.648816016</v>
+        <v>1566.000800684</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09848707199368925</v>
+        <v>0.09896097529041903</v>
       </c>
       <c r="T14">
-        <v>1.083301654294353</v>
+        <v>1.09304560486698</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.65282276897834</v>
+        <v>24.60260563290308</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09106568850266455</v>
+        <v>0.09087539365088255</v>
       </c>
       <c r="C15">
-        <v>5243.541368674399</v>
+        <v>5198.580665057194</v>
       </c>
       <c r="D15">
-        <v>5757.938368674399</v>
+        <v>5782.246665057193</v>
       </c>
       <c r="E15">
-        <v>-2772.803</v>
+        <v>-2703.534</v>
       </c>
       <c r="F15">
-        <v>900.497</v>
+        <v>969.7660000000001</v>
       </c>
       <c r="G15">
         <v>386.1</v>
@@ -2523,28 +2523,28 @@
         <v>1114.375</v>
       </c>
       <c r="M15">
-        <v>45.2949991</v>
+        <v>48.7792298</v>
       </c>
       <c r="N15">
-        <v>1069.0800009</v>
+        <v>1065.5957702</v>
       </c>
       <c r="O15">
-        <v>256.5792002159999</v>
+        <v>255.742984848</v>
       </c>
       <c r="P15">
-        <v>812.5008006839998</v>
+        <v>809.8527853519998</v>
       </c>
       <c r="Q15">
-        <v>1566.000800684</v>
+        <v>1563.352785352</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09896097529041903</v>
+        <v>0.09944589959404948</v>
       </c>
       <c r="T15">
-        <v>1.09304560486698</v>
+        <v>1.103016158941295</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.60260563290308</v>
+        <v>22.84527665912428</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09087539365088255</v>
+        <v>0.09068509879910056</v>
       </c>
       <c r="C16">
-        <v>5198.580665057194</v>
+        <v>5153.826076332502</v>
       </c>
       <c r="D16">
-        <v>5782.246665057193</v>
+        <v>5806.761076332502</v>
       </c>
       <c r="E16">
-        <v>-2703.534</v>
+        <v>-2634.265</v>
       </c>
       <c r="F16">
-        <v>969.7660000000001</v>
+        <v>1039.035</v>
       </c>
       <c r="G16">
         <v>386.1</v>
@@ -2605,28 +2605,28 @@
         <v>1114.375</v>
       </c>
       <c r="M16">
-        <v>48.7792298</v>
+        <v>52.2634605</v>
       </c>
       <c r="N16">
-        <v>1065.5957702</v>
+        <v>1062.1115395</v>
       </c>
       <c r="O16">
-        <v>255.742984848</v>
+        <v>254.9067694799999</v>
       </c>
       <c r="P16">
-        <v>809.8527853519998</v>
+        <v>807.2047700199998</v>
       </c>
       <c r="Q16">
-        <v>1563.352785352</v>
+        <v>1560.70477002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09944589959404948</v>
+        <v>0.09994223388129478</v>
       </c>
       <c r="T16">
-        <v>1.103016158941295</v>
+        <v>1.113221314287947</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.84527665912428</v>
+        <v>21.32225821518266</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09068509879910056</v>
+        <v>0.09049480394731857</v>
       </c>
       <c r="C17">
-        <v>5153.826076332502</v>
+        <v>5109.280235195813</v>
       </c>
       <c r="D17">
-        <v>5806.761076332502</v>
+        <v>5831.484235195813</v>
       </c>
       <c r="E17">
-        <v>-2634.265</v>
+        <v>-2564.996</v>
       </c>
       <c r="F17">
-        <v>1039.035</v>
+        <v>1108.304</v>
       </c>
       <c r="G17">
         <v>386.1</v>
@@ -2687,28 +2687,28 @@
         <v>1114.375</v>
       </c>
       <c r="M17">
-        <v>52.26346049999999</v>
+        <v>55.74769119999999</v>
       </c>
       <c r="N17">
-        <v>1062.1115395</v>
+        <v>1058.6273088</v>
       </c>
       <c r="O17">
-        <v>254.9067694799999</v>
+        <v>254.0705541119999</v>
       </c>
       <c r="P17">
-        <v>807.2047700199998</v>
+        <v>804.5567546879998</v>
       </c>
       <c r="Q17">
-        <v>1560.70477002</v>
+        <v>1558.056754688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09994223388129478</v>
+        <v>0.1004503856515697</v>
       </c>
       <c r="T17">
-        <v>1.113221314287947</v>
+        <v>1.123669449523805</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.32225821518267</v>
+        <v>19.98961707673375</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09049480394731857</v>
+        <v>0.09030450909553658</v>
       </c>
       <c r="C18">
-        <v>5109.280235195813</v>
+        <v>5064.94581937072</v>
       </c>
       <c r="D18">
-        <v>5831.484235195813</v>
+        <v>5856.41881937072</v>
       </c>
       <c r="E18">
-        <v>-2564.996</v>
+        <v>-2495.727</v>
       </c>
       <c r="F18">
-        <v>1108.304</v>
+        <v>1177.573</v>
       </c>
       <c r="G18">
         <v>386.1</v>
@@ -2769,28 +2769,28 @@
         <v>1114.375</v>
       </c>
       <c r="M18">
-        <v>55.74769119999999</v>
+        <v>59.2319219</v>
       </c>
       <c r="N18">
-        <v>1058.6273088</v>
+        <v>1055.1430781</v>
       </c>
       <c r="O18">
-        <v>254.0705541119999</v>
+        <v>253.2343387439999</v>
       </c>
       <c r="P18">
-        <v>804.5567546879998</v>
+        <v>801.9087393559997</v>
       </c>
       <c r="Q18">
-        <v>1558.056754688</v>
+        <v>1555.408739356</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1004503856515697</v>
+        <v>0.1009707820428152</v>
       </c>
       <c r="T18">
-        <v>1.123669449523805</v>
+        <v>1.134369347054503</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.98961707673375</v>
+        <v>18.81375724869059</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09030450909553658</v>
+        <v>0.0901142142437546</v>
       </c>
       <c r="C19">
-        <v>5064.94581937072</v>
+        <v>5020.825552575719</v>
       </c>
       <c r="D19">
-        <v>5856.41881937072</v>
+        <v>5881.56755257572</v>
       </c>
       <c r="E19">
-        <v>-2495.727</v>
+        <v>-2426.458</v>
       </c>
       <c r="F19">
-        <v>1177.573</v>
+        <v>1246.842</v>
       </c>
       <c r="G19">
         <v>386.1</v>
@@ -2851,28 +2851,28 @@
         <v>1114.375</v>
       </c>
       <c r="M19">
-        <v>59.2319219</v>
+        <v>62.7161526</v>
       </c>
       <c r="N19">
-        <v>1055.1430781</v>
+        <v>1051.6588474</v>
       </c>
       <c r="O19">
-        <v>253.2343387439999</v>
+        <v>252.3981233759999</v>
       </c>
       <c r="P19">
-        <v>801.9087393559997</v>
+        <v>799.2607240239998</v>
       </c>
       <c r="Q19">
-        <v>1555.408739356</v>
+        <v>1552.760724024</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1009707820428152</v>
+        <v>0.101503871028969</v>
       </c>
       <c r="T19">
-        <v>1.134369347054503</v>
+        <v>1.145330217695706</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.81375724869059</v>
+        <v>17.76854851265222</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0901142142437546</v>
+        <v>0.0899239193919726</v>
       </c>
       <c r="C20">
-        <v>5020.82555257572</v>
+        <v>4976.922205516035</v>
       </c>
       <c r="D20">
-        <v>5881.56755257572</v>
+        <v>5906.933205516035</v>
       </c>
       <c r="E20">
-        <v>-2426.458000000001</v>
+        <v>-2357.189</v>
       </c>
       <c r="F20">
-        <v>1246.842</v>
+        <v>1316.111</v>
       </c>
       <c r="G20">
         <v>386.1</v>
@@ -2933,28 +2933,28 @@
         <v>1114.375</v>
       </c>
       <c r="M20">
-        <v>62.71615259999999</v>
+        <v>66.20038329999998</v>
       </c>
       <c r="N20">
-        <v>1051.6588474</v>
+        <v>1048.1746167</v>
       </c>
       <c r="O20">
-        <v>252.3981233759999</v>
+        <v>251.561908008</v>
       </c>
       <c r="P20">
-        <v>799.2607240239998</v>
+        <v>796.612708692</v>
       </c>
       <c r="Q20">
-        <v>1552.760724024</v>
+        <v>1550.112708692</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.101503871028969</v>
+        <v>0.102050122706139</v>
       </c>
       <c r="T20">
-        <v>1.145330217695706</v>
+        <v>1.156561727118173</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.76854851265222</v>
+        <v>16.83336174882843</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0899239193919726</v>
+        <v>0.0897336245401906</v>
       </c>
       <c r="C21">
-        <v>4976.922205516035</v>
+        <v>4933.238596901205</v>
       </c>
       <c r="D21">
-        <v>5906.933205516035</v>
+        <v>5932.518596901205</v>
       </c>
       <c r="E21">
-        <v>-2357.189</v>
+        <v>-2287.92</v>
       </c>
       <c r="F21">
-        <v>1316.111</v>
+        <v>1385.38</v>
       </c>
       <c r="G21">
         <v>386.1</v>
@@ -3015,28 +3015,28 @@
         <v>1114.375</v>
       </c>
       <c r="M21">
-        <v>66.20038329999998</v>
+        <v>69.684614</v>
       </c>
       <c r="N21">
-        <v>1048.1746167</v>
+        <v>1044.690386</v>
       </c>
       <c r="O21">
-        <v>251.561908008</v>
+        <v>250.7256926399999</v>
       </c>
       <c r="P21">
-        <v>796.612708692</v>
+        <v>793.9646933599998</v>
       </c>
       <c r="Q21">
-        <v>1550.112708692</v>
+        <v>1547.46469336</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.102050122706139</v>
+        <v>0.1026100306752382</v>
       </c>
       <c r="T21">
-        <v>1.156561727118173</v>
+        <v>1.168074024276202</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.83336174882843</v>
+        <v>15.991693661387</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0897336245401906</v>
+        <v>0.08954332968840861</v>
       </c>
       <c r="C22">
-        <v>4933.238596901205</v>
+        <v>4889.777594489242</v>
       </c>
       <c r="D22">
-        <v>5932.518596901205</v>
+        <v>5958.326594489242</v>
       </c>
       <c r="E22">
-        <v>-2287.92</v>
+        <v>-2218.651</v>
       </c>
       <c r="F22">
-        <v>1385.38</v>
+        <v>1454.649</v>
       </c>
       <c r="G22">
         <v>386.1</v>
@@ -3097,28 +3097,28 @@
         <v>1114.375</v>
       </c>
       <c r="M22">
-        <v>69.684614</v>
+        <v>73.16884470000001</v>
       </c>
       <c r="N22">
-        <v>1044.690386</v>
+        <v>1041.2061553</v>
       </c>
       <c r="O22">
-        <v>250.7256926399999</v>
+        <v>249.889477272</v>
       </c>
       <c r="P22">
-        <v>793.9646933599998</v>
+        <v>791.3166780279998</v>
       </c>
       <c r="Q22">
-        <v>1547.46469336</v>
+        <v>1544.816678028</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1026100306752382</v>
+        <v>0.1031841135296312</v>
       </c>
       <c r="T22">
-        <v>1.168074024276202</v>
+        <v>1.179877771995193</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.991693661387</v>
+        <v>15.23018443941619</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08954332968840861</v>
+        <v>0.08935303483662663</v>
       </c>
       <c r="C23">
-        <v>4889.777594489242</v>
+        <v>4846.542116158173</v>
       </c>
       <c r="D23">
-        <v>5958.326594489242</v>
+        <v>5984.360116158172</v>
       </c>
       <c r="E23">
-        <v>-2218.651</v>
+        <v>-2149.382000000001</v>
       </c>
       <c r="F23">
-        <v>1454.649</v>
+        <v>1523.918</v>
       </c>
       <c r="G23">
         <v>386.1</v>
@@ -3179,28 +3179,28 @@
         <v>1114.375</v>
       </c>
       <c r="M23">
-        <v>73.16884469999999</v>
+        <v>76.65307539999999</v>
       </c>
       <c r="N23">
-        <v>1041.2061553</v>
+        <v>1037.7219246</v>
       </c>
       <c r="O23">
-        <v>249.889477272</v>
+        <v>249.0532619039999</v>
       </c>
       <c r="P23">
-        <v>791.3166780279998</v>
+        <v>788.6686626959998</v>
       </c>
       <c r="Q23">
-        <v>1544.816678028</v>
+        <v>1542.168662696</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1031841135296312</v>
+        <v>0.1037729164572136</v>
       </c>
       <c r="T23">
-        <v>1.179877771995193</v>
+        <v>1.191984179912108</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.23018443941619</v>
+        <v>14.53790332853364</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08935303483662663</v>
+        <v>0.08916273998484463</v>
       </c>
       <c r="C24">
-        <v>4846.542116158173</v>
+        <v>4803.535131005769</v>
       </c>
       <c r="D24">
-        <v>5984.360116158172</v>
+        <v>6010.622131005768</v>
       </c>
       <c r="E24">
-        <v>-2149.382000000001</v>
+        <v>-2080.113</v>
       </c>
       <c r="F24">
-        <v>1523.918</v>
+        <v>1593.187</v>
       </c>
       <c r="G24">
         <v>386.1</v>
@@ -3261,28 +3261,28 @@
         <v>1114.375</v>
       </c>
       <c r="M24">
-        <v>76.65307539999999</v>
+        <v>80.13730609999999</v>
       </c>
       <c r="N24">
-        <v>1037.7219246</v>
+        <v>1034.2376939</v>
       </c>
       <c r="O24">
-        <v>249.0532619039999</v>
+        <v>248.2170465359999</v>
       </c>
       <c r="P24">
-        <v>788.6686626959998</v>
+        <v>786.0206473639998</v>
       </c>
       <c r="Q24">
-        <v>1542.168662696</v>
+        <v>1539.520647364</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1037729164572136</v>
+        <v>0.1043770129673307</v>
       </c>
       <c r="T24">
-        <v>1.191984179912108</v>
+        <v>1.204405039982708</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.53790332853364</v>
+        <v>13.90582057511913</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08916273998484463</v>
+        <v>0.08897244513306263</v>
       </c>
       <c r="C25">
-        <v>4803.535131005769</v>
+        <v>4760.759660478376</v>
       </c>
       <c r="D25">
-        <v>6010.622131005768</v>
+        <v>6037.115660478376</v>
       </c>
       <c r="E25">
-        <v>-2080.113</v>
+        <v>-2010.844</v>
       </c>
       <c r="F25">
-        <v>1593.187</v>
+        <v>1662.456</v>
       </c>
       <c r="G25">
         <v>386.1</v>
@@ -3343,28 +3343,28 @@
         <v>1114.375</v>
       </c>
       <c r="M25">
-        <v>80.13730609999999</v>
+        <v>83.6215368</v>
       </c>
       <c r="N25">
-        <v>1034.2376939</v>
+        <v>1030.7534632</v>
       </c>
       <c r="O25">
-        <v>248.2170465359999</v>
+        <v>247.3808311679999</v>
       </c>
       <c r="P25">
-        <v>786.0206473639998</v>
+        <v>783.3726320319997</v>
       </c>
       <c r="Q25">
-        <v>1539.520647364</v>
+        <v>1536.872632032</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1043770129673307</v>
+        <v>0.1049970067540298</v>
       </c>
       <c r="T25">
-        <v>1.204405039982708</v>
+        <v>1.217152764792008</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.90582057511913</v>
+        <v>13.32641138448917</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08897244513306263</v>
+        <v>0.08906715028128065</v>
       </c>
       <c r="C26">
-        <v>4760.759660478376</v>
+        <v>4678.276341307412</v>
       </c>
       <c r="D26">
-        <v>6037.115660478376</v>
+        <v>6023.901341307411</v>
       </c>
       <c r="E26">
-        <v>-2010.844</v>
+        <v>-1941.575</v>
       </c>
       <c r="F26">
-        <v>1662.456</v>
+        <v>1731.725</v>
       </c>
       <c r="G26">
         <v>386.1</v>
@@ -3425,45 +3425,45 @@
         <v>1114.375</v>
       </c>
       <c r="M26">
-        <v>83.62153679999999</v>
+        <v>89.70335499999999</v>
       </c>
       <c r="N26">
-        <v>1030.7534632</v>
+        <v>1024.671645</v>
       </c>
       <c r="O26">
-        <v>247.3808311679999</v>
+        <v>245.9211948</v>
       </c>
       <c r="P26">
-        <v>783.3726320319997</v>
+        <v>778.7504501999999</v>
       </c>
       <c r="Q26">
-        <v>1536.872632032</v>
+        <v>1532.2504502</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1049970067540298</v>
+        <v>0.1056335337083742</v>
       </c>
       <c r="T26">
-        <v>1.217152764792008</v>
+        <v>1.230240428929557</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.32641138448917</v>
+        <v>12.42289098328597</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08906715028128065</v>
+        <v>0.08888825542949863</v>
       </c>
       <c r="C27">
-        <v>4678.276341307412</v>
+        <v>4634.017519298162</v>
       </c>
       <c r="D27">
-        <v>6023.901341307411</v>
+        <v>6048.911519298162</v>
       </c>
       <c r="E27">
-        <v>-1941.575</v>
+        <v>-1872.306</v>
       </c>
       <c r="F27">
-        <v>1731.725</v>
+        <v>1800.994</v>
       </c>
       <c r="G27">
         <v>386.1</v>
@@ -3507,28 +3507,28 @@
         <v>1114.375</v>
       </c>
       <c r="M27">
-        <v>89.70335499999999</v>
+        <v>93.29148919999999</v>
       </c>
       <c r="N27">
-        <v>1024.671645</v>
+        <v>1021.0835108</v>
       </c>
       <c r="O27">
-        <v>245.9211948</v>
+        <v>245.0600425919999</v>
       </c>
       <c r="P27">
-        <v>778.7504501999999</v>
+        <v>776.0234682079998</v>
       </c>
       <c r="Q27">
-        <v>1532.2504502</v>
+        <v>1529.523468208</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1056335337083742</v>
+        <v>0.1062872640939171</v>
       </c>
       <c r="T27">
-        <v>1.230240428929557</v>
+        <v>1.243681813719471</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.42289098328597</v>
+        <v>11.94508748392881</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08888825542949863</v>
+        <v>0.08870936057771665</v>
       </c>
       <c r="C28">
-        <v>4634.017519298162</v>
+        <v>4589.967238829702</v>
       </c>
       <c r="D28">
-        <v>6048.911519298162</v>
+        <v>6074.130238829702</v>
       </c>
       <c r="E28">
-        <v>-1872.306</v>
+        <v>-1803.037</v>
       </c>
       <c r="F28">
-        <v>1800.994</v>
+        <v>1870.263</v>
       </c>
       <c r="G28">
         <v>386.1</v>
@@ -3589,28 +3589,28 @@
         <v>1114.375</v>
       </c>
       <c r="M28">
-        <v>93.29148919999999</v>
+        <v>96.8796234</v>
       </c>
       <c r="N28">
-        <v>1021.0835108</v>
+        <v>1017.4953766</v>
       </c>
       <c r="O28">
-        <v>245.0600425919999</v>
+        <v>244.1988903839999</v>
       </c>
       <c r="P28">
-        <v>776.0234682079998</v>
+        <v>773.2964862159998</v>
       </c>
       <c r="Q28">
-        <v>1529.523468208</v>
+        <v>1526.796486216</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1062872640939171</v>
+        <v>0.1069589049009817</v>
       </c>
       <c r="T28">
-        <v>1.243681813719471</v>
+        <v>1.257491455626918</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.94508748392881</v>
+        <v>11.50267683637589</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08870936057771665</v>
+        <v>0.08853046572593465</v>
       </c>
       <c r="C29">
-        <v>4589.967238829702</v>
+        <v>4546.128119134529</v>
       </c>
       <c r="D29">
-        <v>6074.130238829702</v>
+        <v>6099.560119134529</v>
       </c>
       <c r="E29">
-        <v>-1803.037</v>
+        <v>-1733.768</v>
       </c>
       <c r="F29">
-        <v>1870.263</v>
+        <v>1939.532</v>
       </c>
       <c r="G29">
         <v>386.1</v>
@@ -3671,28 +3671,28 @@
         <v>1114.375</v>
       </c>
       <c r="M29">
-        <v>96.8796234</v>
+        <v>100.4677576</v>
       </c>
       <c r="N29">
-        <v>1017.4953766</v>
+        <v>1013.9072424</v>
       </c>
       <c r="O29">
-        <v>244.1988903839999</v>
+        <v>243.3377381759999</v>
       </c>
       <c r="P29">
-        <v>773.2964862159998</v>
+        <v>770.5695042239998</v>
       </c>
       <c r="Q29">
-        <v>1526.796486216</v>
+        <v>1524.069504224</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1069589049009817</v>
+        <v>0.1076492023971315</v>
       </c>
       <c r="T29">
-        <v>1.257491455626918</v>
+        <v>1.27168469869846</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.50267683637589</v>
+        <v>11.09186694936247</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08853046572593465</v>
+        <v>0.08835157087415267</v>
       </c>
       <c r="C30">
-        <v>4546.128119134529</v>
+        <v>4502.502823492119</v>
       </c>
       <c r="D30">
-        <v>6099.560119134529</v>
+        <v>6125.203823492119</v>
       </c>
       <c r="E30">
-        <v>-1733.768</v>
+        <v>-1664.499</v>
       </c>
       <c r="F30">
-        <v>1939.532</v>
+        <v>2008.801</v>
       </c>
       <c r="G30">
         <v>386.1</v>
@@ -3753,28 +3753,28 @@
         <v>1114.375</v>
       </c>
       <c r="M30">
-        <v>100.4677576</v>
+        <v>104.0558918</v>
       </c>
       <c r="N30">
-        <v>1013.9072424</v>
+        <v>1010.3191082</v>
       </c>
       <c r="O30">
-        <v>243.3377381759999</v>
+        <v>242.4765859679999</v>
       </c>
       <c r="P30">
-        <v>770.5695042239998</v>
+        <v>767.8425222319997</v>
       </c>
       <c r="Q30">
-        <v>1524.069504224</v>
+        <v>1521.342522232</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1076492023971315</v>
+        <v>0.1083589448931728</v>
       </c>
       <c r="T30">
-        <v>1.27168469869846</v>
+        <v>1.28627775143399</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.09186694936247</v>
+        <v>10.70938877869479</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08835157087415267</v>
+        <v>0.08817267602237065</v>
       </c>
       <c r="C31">
-        <v>4502.50282349212</v>
+        <v>4459.094060158781</v>
       </c>
       <c r="D31">
-        <v>6125.203823492119</v>
+        <v>6151.06406015878</v>
       </c>
       <c r="E31">
-        <v>-1664.499</v>
+        <v>-1595.23</v>
       </c>
       <c r="F31">
-        <v>2008.801</v>
+        <v>2078.07</v>
       </c>
       <c r="G31">
         <v>386.1</v>
@@ -3835,28 +3835,28 @@
         <v>1114.375</v>
       </c>
       <c r="M31">
-        <v>104.0558918</v>
+        <v>107.644026</v>
       </c>
       <c r="N31">
-        <v>1010.3191082</v>
+        <v>1006.730974</v>
       </c>
       <c r="O31">
-        <v>242.476585968</v>
+        <v>241.6154337599999</v>
       </c>
       <c r="P31">
-        <v>767.8425222319999</v>
+        <v>765.1155402399999</v>
       </c>
       <c r="Q31">
-        <v>1521.342522232</v>
+        <v>1518.61554024</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1083589448931728</v>
+        <v>0.1090889657462438</v>
       </c>
       <c r="T31">
-        <v>1.28627775143399</v>
+        <v>1.301287748533391</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.7093887786948</v>
+        <v>10.3524091527383</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08817267602237065</v>
+        <v>0.08799378117058868</v>
       </c>
       <c r="C32">
-        <v>4459.094060158781</v>
+        <v>4415.904583321085</v>
       </c>
       <c r="D32">
-        <v>6151.06406015878</v>
+        <v>6177.143583321084</v>
       </c>
       <c r="E32">
-        <v>-1595.23</v>
+        <v>-1525.961</v>
       </c>
       <c r="F32">
-        <v>2078.07</v>
+        <v>2147.339</v>
       </c>
       <c r="G32">
         <v>386.1</v>
@@ -3917,28 +3917,28 @@
         <v>1114.375</v>
       </c>
       <c r="M32">
-        <v>107.644026</v>
+        <v>111.2321602</v>
       </c>
       <c r="N32">
-        <v>1006.730974</v>
+        <v>1003.1428398</v>
       </c>
       <c r="O32">
-        <v>241.6154337599999</v>
+        <v>240.754281552</v>
       </c>
       <c r="P32">
-        <v>765.1155402399999</v>
+        <v>762.3885582479999</v>
       </c>
       <c r="Q32">
-        <v>1518.61554024</v>
+        <v>1515.888558248</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1090889657462438</v>
+        <v>0.1098401466240416</v>
       </c>
       <c r="T32">
-        <v>1.301287748533391</v>
+        <v>1.316732818012486</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.3524091527383</v>
+        <v>10.01846047039191</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08799378117058868</v>
+        <v>0.08822832631880667</v>
       </c>
       <c r="C33">
-        <v>4415.904583321085</v>
+        <v>4312.488135542273</v>
       </c>
       <c r="D33">
-        <v>6177.143583321084</v>
+        <v>6142.996135542272</v>
       </c>
       <c r="E33">
-        <v>-1525.961</v>
+        <v>-1456.692</v>
       </c>
       <c r="F33">
-        <v>2147.339</v>
+        <v>2216.608</v>
       </c>
       <c r="G33">
         <v>386.1</v>
@@ -3999,45 +3999,45 @@
         <v>1114.375</v>
       </c>
       <c r="M33">
-        <v>111.2321602</v>
+        <v>118.588528</v>
       </c>
       <c r="N33">
-        <v>1003.1428398</v>
+        <v>995.7864719999998</v>
       </c>
       <c r="O33">
-        <v>240.754281552</v>
+        <v>238.9887532799999</v>
       </c>
       <c r="P33">
-        <v>762.3885582479999</v>
+        <v>756.7977187199998</v>
       </c>
       <c r="Q33">
-        <v>1515.888558248</v>
+        <v>1510.29771872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1098401466240416</v>
+        <v>0.1106134210570686</v>
       </c>
       <c r="T33">
-        <v>1.316732818012486</v>
+        <v>1.332632154240966</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.01846047039191</v>
+        <v>9.396988214576707</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08822832631880667</v>
+        <v>0.08806235146702468</v>
       </c>
       <c r="C34">
-        <v>4312.488135542273</v>
+        <v>4267.34422176445</v>
       </c>
       <c r="D34">
-        <v>6142.996135542272</v>
+        <v>6167.12122176445</v>
       </c>
       <c r="E34">
-        <v>-1456.692</v>
+        <v>-1387.423</v>
       </c>
       <c r="F34">
-        <v>2216.608</v>
+        <v>2285.877</v>
       </c>
       <c r="G34">
         <v>386.1</v>
@@ -4081,28 +4081,28 @@
         <v>1114.375</v>
       </c>
       <c r="M34">
-        <v>118.588528</v>
+        <v>122.2944195</v>
       </c>
       <c r="N34">
-        <v>995.7864719999998</v>
+        <v>992.0805804999998</v>
       </c>
       <c r="O34">
-        <v>238.9887532799999</v>
+        <v>238.0993393199999</v>
       </c>
       <c r="P34">
-        <v>756.7977187199998</v>
+        <v>753.9812411799999</v>
       </c>
       <c r="Q34">
-        <v>1510.29771872</v>
+        <v>1507.48124118</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1106134210570686</v>
+        <v>0.1114097783089921</v>
       </c>
       <c r="T34">
-        <v>1.332632154240966</v>
+        <v>1.349006097521041</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.396988214576707</v>
+        <v>9.112230995953171</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08806235146702468</v>
+        <v>0.08789637661524269</v>
       </c>
       <c r="C35">
-        <v>4267.34422176445</v>
+        <v>4222.390545623779</v>
       </c>
       <c r="D35">
-        <v>6167.12122176445</v>
+        <v>6191.436545623779</v>
       </c>
       <c r="E35">
-        <v>-1387.423</v>
+        <v>-1318.154</v>
       </c>
       <c r="F35">
-        <v>2285.877</v>
+        <v>2355.146</v>
       </c>
       <c r="G35">
         <v>386.1</v>
@@ -4163,28 +4163,28 @@
         <v>1114.375</v>
       </c>
       <c r="M35">
-        <v>122.2944195</v>
+        <v>126.000311</v>
       </c>
       <c r="N35">
-        <v>992.0805804999998</v>
+        <v>988.3746889999998</v>
       </c>
       <c r="O35">
-        <v>238.0993393199999</v>
+        <v>237.2099253599999</v>
       </c>
       <c r="P35">
-        <v>753.9812411799999</v>
+        <v>751.1647636399998</v>
       </c>
       <c r="Q35">
-        <v>1507.48124118</v>
+        <v>1504.66476364</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1114097783089921</v>
+        <v>0.1122302675988526</v>
       </c>
       <c r="T35">
-        <v>1.349006097521041</v>
+        <v>1.365876220900514</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.112230995953171</v>
+        <v>8.844224201954546</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08789637661524269</v>
+        <v>0.0877304017634607</v>
       </c>
       <c r="C36">
-        <v>4222.390545623779</v>
+        <v>4177.629366196895</v>
       </c>
       <c r="D36">
-        <v>6191.436545623779</v>
+        <v>6215.944366196894</v>
       </c>
       <c r="E36">
-        <v>-1318.154</v>
+        <v>-1248.885</v>
       </c>
       <c r="F36">
-        <v>2355.146</v>
+        <v>2424.415</v>
       </c>
       <c r="G36">
         <v>386.1</v>
@@ -4245,28 +4245,28 @@
         <v>1114.375</v>
       </c>
       <c r="M36">
-        <v>126.000311</v>
+        <v>129.7062025</v>
       </c>
       <c r="N36">
-        <v>988.3746889999998</v>
+        <v>984.6687974999998</v>
       </c>
       <c r="O36">
-        <v>237.2099253599999</v>
+        <v>236.3205113999999</v>
       </c>
       <c r="P36">
-        <v>751.1647636399998</v>
+        <v>748.3482860999998</v>
       </c>
       <c r="Q36">
-        <v>1504.66476364</v>
+        <v>1501.8482861</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1122302675988526</v>
+        <v>0.1130760027130165</v>
       </c>
       <c r="T36">
-        <v>1.365876220900514</v>
+        <v>1.383265424999355</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.844224201954546</v>
+        <v>8.591532081898704</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0877304017634607</v>
+        <v>0.08756442691167872</v>
       </c>
       <c r="C37">
-        <v>4177.629366196895</v>
+        <v>4133.062978471362</v>
       </c>
       <c r="D37">
-        <v>6215.944366196894</v>
+        <v>6240.646978471362</v>
       </c>
       <c r="E37">
-        <v>-1248.885</v>
+        <v>-1179.616</v>
       </c>
       <c r="F37">
-        <v>2424.415</v>
+        <v>2493.684</v>
       </c>
       <c r="G37">
         <v>386.1</v>
@@ -4327,28 +4327,28 @@
         <v>1114.375</v>
       </c>
       <c r="M37">
-        <v>129.7062025</v>
+        <v>133.412094</v>
       </c>
       <c r="N37">
-        <v>984.6687974999998</v>
+        <v>980.9629059999997</v>
       </c>
       <c r="O37">
-        <v>236.3205113999999</v>
+        <v>235.4310974399999</v>
       </c>
       <c r="P37">
-        <v>748.3482860999998</v>
+        <v>745.5318085599998</v>
       </c>
       <c r="Q37">
-        <v>1501.8482861</v>
+        <v>1499.03180856</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1130760027130165</v>
+        <v>0.113948167049498</v>
       </c>
       <c r="T37">
-        <v>1.383265424999355</v>
+        <v>1.401198041726284</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.591532081898704</v>
+        <v>8.352878412957072</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08756442691167871</v>
+        <v>0.08739845205989671</v>
       </c>
       <c r="C38">
-        <v>4133.062978471364</v>
+        <v>4088.693714062105</v>
       </c>
       <c r="D38">
-        <v>6240.646978471364</v>
+        <v>6265.546714062105</v>
       </c>
       <c r="E38">
-        <v>-1179.616</v>
+        <v>-1110.347</v>
       </c>
       <c r="F38">
-        <v>2493.684</v>
+        <v>2562.953</v>
       </c>
       <c r="G38">
         <v>386.1</v>
@@ -4409,28 +4409,28 @@
         <v>1114.375</v>
       </c>
       <c r="M38">
-        <v>133.412094</v>
+        <v>137.1179855</v>
       </c>
       <c r="N38">
-        <v>980.9629059999997</v>
+        <v>977.2570144999997</v>
       </c>
       <c r="O38">
-        <v>235.4310974399999</v>
+        <v>234.5416834799999</v>
       </c>
       <c r="P38">
-        <v>745.5318085599998</v>
+        <v>742.7153310199998</v>
       </c>
       <c r="Q38">
-        <v>1499.03180856</v>
+        <v>1496.21533102</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.113948167049498</v>
+        <v>0.1148480191426932</v>
       </c>
       <c r="T38">
-        <v>1.401198041726284</v>
+        <v>1.419699947873116</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.352878412957072</v>
+        <v>8.127124942336611</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08739845205989671</v>
+        <v>0.08723247720811474</v>
       </c>
       <c r="C39">
-        <v>4088.693714062105</v>
+        <v>4044.523941945004</v>
       </c>
       <c r="D39">
-        <v>6265.546714062105</v>
+        <v>6290.645941945004</v>
       </c>
       <c r="E39">
-        <v>-1110.347</v>
+        <v>-1041.078</v>
       </c>
       <c r="F39">
-        <v>2562.953</v>
+        <v>2632.222</v>
       </c>
       <c r="G39">
         <v>386.1</v>
@@ -4491,28 +4491,28 @@
         <v>1114.375</v>
       </c>
       <c r="M39">
-        <v>137.1179855</v>
+        <v>140.823877</v>
       </c>
       <c r="N39">
-        <v>977.2570144999997</v>
+        <v>973.5511229999997</v>
       </c>
       <c r="O39">
-        <v>234.5416834799999</v>
+        <v>233.6522695199999</v>
       </c>
       <c r="P39">
-        <v>742.7153310199998</v>
+        <v>739.8988534799998</v>
       </c>
       <c r="Q39">
-        <v>1496.21533102</v>
+        <v>1493.39885348</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1148480191426932</v>
+        <v>0.1157768987227657</v>
       </c>
       <c r="T39">
-        <v>1.419699947873116</v>
+        <v>1.438798689702104</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.127124942336611</v>
+        <v>7.913253233327754</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08723247720811474</v>
+        <v>0.08706650235633273</v>
       </c>
       <c r="C40">
-        <v>4044.523941945004</v>
+        <v>4000.556069208269</v>
       </c>
       <c r="D40">
-        <v>6290.645941945004</v>
+        <v>6315.947069208269</v>
       </c>
       <c r="E40">
-        <v>-1041.078</v>
+        <v>-971.8090000000002</v>
       </c>
       <c r="F40">
-        <v>2632.222</v>
+        <v>2701.491</v>
       </c>
       <c r="G40">
         <v>386.1</v>
@@ -4573,28 +4573,28 @@
         <v>1114.375</v>
       </c>
       <c r="M40">
-        <v>140.823877</v>
+        <v>144.5297685</v>
       </c>
       <c r="N40">
-        <v>973.5511229999997</v>
+        <v>969.8452314999997</v>
       </c>
       <c r="O40">
-        <v>233.6522695199999</v>
+        <v>232.7628555599999</v>
       </c>
       <c r="P40">
-        <v>739.8988534799998</v>
+        <v>737.0823759399998</v>
       </c>
       <c r="Q40">
-        <v>1493.39885348</v>
+        <v>1490.58237594</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1157768987227657</v>
+        <v>0.1167362333710373</v>
       </c>
       <c r="T40">
-        <v>1.438798689702104</v>
+        <v>1.45852361978778</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.913253233327754</v>
+        <v>7.710349304268068</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08706650235633273</v>
+        <v>0.08714372750455074</v>
       </c>
       <c r="C41">
-        <v>4000.556069208269</v>
+        <v>3919.489633950332</v>
       </c>
       <c r="D41">
-        <v>6315.947069208269</v>
+        <v>6304.149633950332</v>
       </c>
       <c r="E41">
-        <v>-971.8090000000002</v>
+        <v>-902.54</v>
       </c>
       <c r="F41">
-        <v>2701.491</v>
+        <v>2770.76</v>
       </c>
       <c r="G41">
         <v>386.1</v>
@@ -4655,45 +4655,45 @@
         <v>1114.375</v>
       </c>
       <c r="M41">
-        <v>144.5297685</v>
+        <v>150.452268</v>
       </c>
       <c r="N41">
-        <v>969.8452314999997</v>
+        <v>963.9227319999998</v>
       </c>
       <c r="O41">
-        <v>232.7628555599999</v>
+        <v>231.3414556799999</v>
       </c>
       <c r="P41">
-        <v>737.0823759399998</v>
+        <v>732.5812763199998</v>
       </c>
       <c r="Q41">
-        <v>1490.58237594</v>
+        <v>1486.08127632</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1167362333710373</v>
+        <v>0.1177275458409179</v>
       </c>
       <c r="T41">
-        <v>1.45852361978778</v>
+        <v>1.478906047542978</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.710349304268068</v>
+        <v>7.406834172815525</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08714372750455074</v>
+        <v>0.08698383265276874</v>
       </c>
       <c r="C42">
-        <v>3919.489633950332</v>
+        <v>3874.696283893619</v>
       </c>
       <c r="D42">
-        <v>6304.149633950332</v>
+        <v>6328.625283893619</v>
       </c>
       <c r="E42">
-        <v>-902.54</v>
+        <v>-833.2710000000002</v>
       </c>
       <c r="F42">
-        <v>2770.76</v>
+        <v>2840.029</v>
       </c>
       <c r="G42">
         <v>386.1</v>
@@ -4737,28 +4737,28 @@
         <v>1114.375</v>
       </c>
       <c r="M42">
-        <v>150.452268</v>
+        <v>154.2135747</v>
       </c>
       <c r="N42">
-        <v>963.9227319999998</v>
+        <v>960.1614252999998</v>
       </c>
       <c r="O42">
-        <v>231.3414556799999</v>
+        <v>230.4387420719999</v>
       </c>
       <c r="P42">
-        <v>732.5812763199998</v>
+        <v>729.7226832279998</v>
       </c>
       <c r="Q42">
-        <v>1486.08127632</v>
+        <v>1483.222683228</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1177275458409179</v>
+        <v>0.1187524621233368</v>
       </c>
       <c r="T42">
-        <v>1.478906047542978</v>
+        <v>1.49997940505259</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.406834172815525</v>
+        <v>7.226179680795634</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08698383265276874</v>
+        <v>0.08682393780098674</v>
       </c>
       <c r="C43">
-        <v>3874.696283893619</v>
+        <v>3830.093726365838</v>
       </c>
       <c r="D43">
-        <v>6328.625283893619</v>
+        <v>6353.291726365838</v>
       </c>
       <c r="E43">
-        <v>-833.2710000000002</v>
+        <v>-764.002</v>
       </c>
       <c r="F43">
-        <v>2840.029</v>
+        <v>2909.298</v>
       </c>
       <c r="G43">
         <v>386.1</v>
@@ -4819,28 +4819,28 @@
         <v>1114.375</v>
       </c>
       <c r="M43">
-        <v>154.2135747</v>
+        <v>157.9748814</v>
       </c>
       <c r="N43">
-        <v>960.1614252999998</v>
+        <v>956.4001185999998</v>
       </c>
       <c r="O43">
-        <v>230.4387420719999</v>
+        <v>229.5360284639999</v>
       </c>
       <c r="P43">
-        <v>729.7226832279998</v>
+        <v>726.8640901359998</v>
       </c>
       <c r="Q43">
-        <v>1483.222683228</v>
+        <v>1480.364090136</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1187524621233368</v>
+        <v>0.1198127203465289</v>
       </c>
       <c r="T43">
-        <v>1.49997940505259</v>
+        <v>1.521779430062533</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.226179680795634</v>
+        <v>7.054127783633834</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08682393780098675</v>
+        <v>0.08666404294920475</v>
       </c>
       <c r="C44">
-        <v>3830.093726365837</v>
+        <v>3785.68420099437</v>
       </c>
       <c r="D44">
-        <v>6353.291726365836</v>
+        <v>6378.15120099437</v>
       </c>
       <c r="E44">
-        <v>-764.0020000000004</v>
+        <v>-694.7330000000002</v>
       </c>
       <c r="F44">
-        <v>2909.298</v>
+        <v>2978.567</v>
       </c>
       <c r="G44">
         <v>386.1</v>
@@ -4901,28 +4901,28 @@
         <v>1114.375</v>
       </c>
       <c r="M44">
-        <v>157.9748814</v>
+        <v>161.7361881</v>
       </c>
       <c r="N44">
-        <v>956.4001185999998</v>
+        <v>952.6388118999998</v>
       </c>
       <c r="O44">
-        <v>229.5360284639999</v>
+        <v>228.6333148559999</v>
       </c>
       <c r="P44">
-        <v>726.8640901359998</v>
+        <v>724.0054970439999</v>
       </c>
       <c r="Q44">
-        <v>1480.364090136</v>
+        <v>1477.505497044</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1198127203465289</v>
+        <v>0.1209101806126399</v>
       </c>
       <c r="T44">
-        <v>1.521779430062533</v>
+        <v>1.54434436823072</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.054127783633835</v>
+        <v>6.890078300293513</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08666404294920475</v>
+        <v>0.08650414809742277</v>
       </c>
       <c r="C45">
-        <v>3785.68420099437</v>
+        <v>3741.469982597592</v>
       </c>
       <c r="D45">
-        <v>6378.15120099437</v>
+        <v>6403.205982597591</v>
       </c>
       <c r="E45">
-        <v>-694.7330000000002</v>
+        <v>-625.4640000000004</v>
       </c>
       <c r="F45">
-        <v>2978.567</v>
+        <v>3047.836</v>
       </c>
       <c r="G45">
         <v>386.1</v>
@@ -4983,28 +4983,28 @@
         <v>1114.375</v>
       </c>
       <c r="M45">
-        <v>161.7361881</v>
+        <v>165.4974948</v>
       </c>
       <c r="N45">
-        <v>952.6388118999998</v>
+        <v>948.8775051999997</v>
       </c>
       <c r="O45">
-        <v>228.6333148559999</v>
+        <v>227.7306012479999</v>
       </c>
       <c r="P45">
-        <v>724.0054970439999</v>
+        <v>721.1469039519998</v>
       </c>
       <c r="Q45">
-        <v>1477.505497044</v>
+        <v>1474.646903952</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1209101806126399</v>
+        <v>0.1220468358882549</v>
       </c>
       <c r="T45">
-        <v>1.54434436823072</v>
+        <v>1.567715197047771</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.890078300293513</v>
+        <v>6.733485611650478</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08650414809742277</v>
+        <v>0.08634425324564077</v>
       </c>
       <c r="C46">
-        <v>3741.469982597592</v>
+        <v>3697.453381878793</v>
       </c>
       <c r="D46">
-        <v>6403.205982597591</v>
+        <v>6428.458381878792</v>
       </c>
       <c r="E46">
-        <v>-625.4640000000004</v>
+        <v>-556.1950000000002</v>
       </c>
       <c r="F46">
-        <v>3047.836</v>
+        <v>3117.105</v>
       </c>
       <c r="G46">
         <v>386.1</v>
@@ -5065,28 +5065,28 @@
         <v>1114.375</v>
       </c>
       <c r="M46">
-        <v>165.4974948</v>
+        <v>169.2588015</v>
       </c>
       <c r="N46">
-        <v>948.8775051999997</v>
+        <v>945.1161984999998</v>
       </c>
       <c r="O46">
-        <v>227.7306012479999</v>
+        <v>226.8278876399999</v>
       </c>
       <c r="P46">
-        <v>721.1469039519998</v>
+        <v>718.2883108599998</v>
       </c>
       <c r="Q46">
-        <v>1474.646903952</v>
+        <v>1471.78831086</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1220468358882549</v>
+        <v>0.1232248240829832</v>
       </c>
       <c r="T46">
-        <v>1.567715197047771</v>
+        <v>1.591935874185442</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.733485611650478</v>
+        <v>6.583852598058245</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08634425324564077</v>
+        <v>0.0861843583938588</v>
       </c>
       <c r="C47">
-        <v>3697.453381878793</v>
+        <v>3653.636746136569</v>
       </c>
       <c r="D47">
-        <v>6428.458381878792</v>
+        <v>6453.910746136568</v>
       </c>
       <c r="E47">
-        <v>-556.1950000000002</v>
+        <v>-486.9260000000004</v>
       </c>
       <c r="F47">
-        <v>3117.105</v>
+        <v>3186.374</v>
       </c>
       <c r="G47">
         <v>386.1</v>
@@ -5147,28 +5147,28 @@
         <v>1114.375</v>
       </c>
       <c r="M47">
-        <v>169.2588015</v>
+        <v>173.0201082</v>
       </c>
       <c r="N47">
-        <v>945.1161984999998</v>
+        <v>941.3548917999998</v>
       </c>
       <c r="O47">
-        <v>226.8278876399999</v>
+        <v>225.9251740319999</v>
       </c>
       <c r="P47">
-        <v>718.2883108599998</v>
+        <v>715.4297177679998</v>
       </c>
       <c r="Q47">
-        <v>1471.78831086</v>
+        <v>1468.929717768</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1232248240829832</v>
+        <v>0.1244464414701089</v>
       </c>
       <c r="T47">
-        <v>1.591935874185442</v>
+        <v>1.617053613439323</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.583852598058245</v>
+        <v>6.440725367665675</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0861843583938588</v>
+        <v>0.08602446354207678</v>
       </c>
       <c r="C48">
-        <v>3653.636746136569</v>
+        <v>3610.02245999219</v>
       </c>
       <c r="D48">
-        <v>6453.910746136568</v>
+        <v>6479.56545999219</v>
       </c>
       <c r="E48">
-        <v>-486.9260000000004</v>
+        <v>-417.6570000000002</v>
       </c>
       <c r="F48">
-        <v>3186.374</v>
+        <v>3255.643</v>
       </c>
       <c r="G48">
         <v>386.1</v>
@@ -5229,28 +5229,28 @@
         <v>1114.375</v>
       </c>
       <c r="M48">
-        <v>173.0201082</v>
+        <v>176.7814149</v>
       </c>
       <c r="N48">
-        <v>941.3548917999998</v>
+        <v>937.5935850999997</v>
       </c>
       <c r="O48">
-        <v>225.9251740319999</v>
+        <v>225.0224604239999</v>
       </c>
       <c r="P48">
-        <v>715.4297177679998</v>
+        <v>712.5711246759997</v>
       </c>
       <c r="Q48">
-        <v>1468.929717768</v>
+        <v>1466.071124676</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1244464414701089</v>
+        <v>0.12571415762656</v>
       </c>
       <c r="T48">
-        <v>1.617053613439323</v>
+        <v>1.643119191910331</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.440725367665675</v>
+        <v>6.30368865771534</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08602446354207678</v>
+        <v>0.0858645686902948</v>
       </c>
       <c r="C49">
-        <v>3610.02245999219</v>
+        <v>3566.612946134321</v>
       </c>
       <c r="D49">
-        <v>6479.56545999219</v>
+        <v>6505.424946134321</v>
       </c>
       <c r="E49">
-        <v>-417.6570000000002</v>
+        <v>-348.3879999999999</v>
       </c>
       <c r="F49">
-        <v>3255.643</v>
+        <v>3324.912</v>
       </c>
       <c r="G49">
         <v>386.1</v>
@@ -5311,28 +5311,28 @@
         <v>1114.375</v>
       </c>
       <c r="M49">
-        <v>176.7814149</v>
+        <v>180.5427216</v>
       </c>
       <c r="N49">
-        <v>937.5935850999997</v>
+        <v>933.8322783999997</v>
       </c>
       <c r="O49">
-        <v>225.0224604239999</v>
+        <v>224.1197468159999</v>
       </c>
       <c r="P49">
-        <v>712.5711246759997</v>
+        <v>709.7125315839999</v>
       </c>
       <c r="Q49">
-        <v>1466.071124676</v>
+        <v>1463.212531584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.12571415762656</v>
+        <v>0.1270306320967207</v>
       </c>
       <c r="T49">
-        <v>1.643119191910331</v>
+        <v>1.670187292630225</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.30368865771534</v>
+        <v>6.172361810679604</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0858645686902948</v>
+        <v>0.08607707383851279</v>
       </c>
       <c r="C50">
-        <v>3566.612946134321</v>
+        <v>3463.020790039565</v>
       </c>
       <c r="D50">
-        <v>6505.424946134321</v>
+        <v>6471.101790039565</v>
       </c>
       <c r="E50">
-        <v>-348.3880000000004</v>
+        <v>-279.1190000000006</v>
       </c>
       <c r="F50">
-        <v>3324.912</v>
+        <v>3394.181</v>
       </c>
       <c r="G50">
         <v>386.1</v>
@@ -5393,45 +5393,45 @@
         <v>1114.375</v>
       </c>
       <c r="M50">
-        <v>180.5427216</v>
+        <v>187.6982093</v>
       </c>
       <c r="N50">
-        <v>933.8322783999997</v>
+        <v>926.6767906999999</v>
       </c>
       <c r="O50">
-        <v>224.1197468159999</v>
+        <v>222.402429768</v>
       </c>
       <c r="P50">
-        <v>709.7125315839999</v>
+        <v>704.2743609319999</v>
       </c>
       <c r="Q50">
-        <v>1463.212531584</v>
+        <v>1457.774360932</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1270306320967207</v>
+        <v>0.1283987330166917</v>
       </c>
       <c r="T50">
-        <v>1.670187292630225</v>
+        <v>1.698316887495996</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.172361810679605</v>
+        <v>5.937057173618971</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08607707383851279</v>
+        <v>0.08592477898673082</v>
       </c>
       <c r="C51">
-        <v>3463.020790039565</v>
+        <v>3418.31305898278</v>
       </c>
       <c r="D51">
-        <v>6471.101790039565</v>
+        <v>6495.663058982779</v>
       </c>
       <c r="E51">
-        <v>-279.1190000000006</v>
+        <v>-209.8500000000004</v>
       </c>
       <c r="F51">
-        <v>3394.181</v>
+        <v>3463.45</v>
       </c>
       <c r="G51">
         <v>386.1</v>
@@ -5475,28 +5475,28 @@
         <v>1114.375</v>
       </c>
       <c r="M51">
-        <v>187.6982093</v>
+        <v>191.528785</v>
       </c>
       <c r="N51">
-        <v>926.6767906999999</v>
+        <v>922.8462149999998</v>
       </c>
       <c r="O51">
-        <v>222.402429768</v>
+        <v>221.4830915999999</v>
       </c>
       <c r="P51">
-        <v>704.2743609319999</v>
+        <v>701.3631233999998</v>
       </c>
       <c r="Q51">
-        <v>1457.774360932</v>
+        <v>1454.8631234</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1283987330166917</v>
+        <v>0.1298215579734616</v>
       </c>
       <c r="T51">
-        <v>1.698316887495996</v>
+        <v>1.727571666156399</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.937057173618971</v>
+        <v>5.81831603014659</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08592477898673082</v>
+        <v>0.08577248413494883</v>
       </c>
       <c r="C52">
-        <v>3418.31305898278</v>
+        <v>3373.792484410976</v>
       </c>
       <c r="D52">
-        <v>6495.663058982779</v>
+        <v>6520.411484410975</v>
       </c>
       <c r="E52">
-        <v>-209.8500000000004</v>
+        <v>-140.5810000000001</v>
       </c>
       <c r="F52">
-        <v>3463.45</v>
+        <v>3532.719</v>
       </c>
       <c r="G52">
         <v>386.1</v>
@@ -5557,28 +5557,28 @@
         <v>1114.375</v>
       </c>
       <c r="M52">
-        <v>191.528785</v>
+        <v>195.3593607</v>
       </c>
       <c r="N52">
-        <v>922.8462149999998</v>
+        <v>919.0156392999997</v>
       </c>
       <c r="O52">
-        <v>221.4830915999999</v>
+        <v>220.5637534319999</v>
       </c>
       <c r="P52">
-        <v>701.3631233999998</v>
+        <v>698.4518858679999</v>
       </c>
       <c r="Q52">
-        <v>1454.8631234</v>
+        <v>1451.951885868</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1298215579734616</v>
+        <v>0.1313024574182629</v>
       </c>
       <c r="T52">
-        <v>1.727571666156399</v>
+        <v>1.758020517415186</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.81831603014659</v>
+        <v>5.7042314021045</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08577248413494883</v>
+        <v>0.08562018928316681</v>
       </c>
       <c r="C53">
-        <v>3373.792484410976</v>
+        <v>3329.46121369987</v>
       </c>
       <c r="D53">
-        <v>6520.411484410975</v>
+        <v>6545.349213699869</v>
       </c>
       <c r="E53">
-        <v>-140.5810000000001</v>
+        <v>-71.31200000000035</v>
       </c>
       <c r="F53">
-        <v>3532.719</v>
+        <v>3601.988</v>
       </c>
       <c r="G53">
         <v>386.1</v>
@@ -5639,28 +5639,28 @@
         <v>1114.375</v>
       </c>
       <c r="M53">
-        <v>195.3593607</v>
+        <v>199.1899364</v>
       </c>
       <c r="N53">
-        <v>919.0156392999997</v>
+        <v>915.1850635999998</v>
       </c>
       <c r="O53">
-        <v>220.5637534319999</v>
+        <v>219.6444152639999</v>
       </c>
       <c r="P53">
-        <v>698.4518858679999</v>
+        <v>695.5406483359999</v>
       </c>
       <c r="Q53">
-        <v>1451.951885868</v>
+        <v>1449.040648336</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1313024574182629</v>
+        <v>0.1328450610065975</v>
       </c>
       <c r="T53">
-        <v>1.758020517415186</v>
+        <v>1.789738070809754</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.7042314021045</v>
+        <v>5.594534644371722</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08562018928316681</v>
+        <v>0.08546789443138483</v>
       </c>
       <c r="C54">
-        <v>3329.46121369987</v>
+        <v>3285.321427202389</v>
       </c>
       <c r="D54">
-        <v>6545.349213699869</v>
+        <v>6570.478427202389</v>
       </c>
       <c r="E54">
-        <v>-71.31200000000035</v>
+        <v>-2.04300000000012</v>
       </c>
       <c r="F54">
-        <v>3601.988</v>
+        <v>3671.257</v>
       </c>
       <c r="G54">
         <v>386.1</v>
@@ -5721,28 +5721,28 @@
         <v>1114.375</v>
       </c>
       <c r="M54">
-        <v>199.1899364</v>
+        <v>203.0205121</v>
       </c>
       <c r="N54">
-        <v>915.1850635999998</v>
+        <v>911.3544878999998</v>
       </c>
       <c r="O54">
-        <v>219.6444152639999</v>
+        <v>218.7250770959999</v>
       </c>
       <c r="P54">
-        <v>695.5406483359999</v>
+        <v>692.6294108039998</v>
       </c>
       <c r="Q54">
-        <v>1449.040648336</v>
+        <v>1446.129410804</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1328450610065975</v>
+        <v>0.1344533073008188</v>
       </c>
       <c r="T54">
-        <v>1.789738070809754</v>
+        <v>1.822805307327497</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.594534644371722</v>
+        <v>5.488977386930745</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08546789443138483</v>
+        <v>0.08531559957960283</v>
       </c>
       <c r="C55">
-        <v>3285.321427202389</v>
+        <v>3241.37533888419</v>
       </c>
       <c r="D55">
-        <v>6570.478427202389</v>
+        <v>6595.801338884189</v>
       </c>
       <c r="E55">
-        <v>-2.04300000000012</v>
+        <v>67.22599999999966</v>
       </c>
       <c r="F55">
-        <v>3671.257</v>
+        <v>3740.526</v>
       </c>
       <c r="G55">
         <v>386.1</v>
@@ -5803,28 +5803,28 @@
         <v>1114.375</v>
       </c>
       <c r="M55">
-        <v>203.0205121</v>
+        <v>206.8510878</v>
       </c>
       <c r="N55">
-        <v>911.3544878999998</v>
+        <v>907.5239121999998</v>
       </c>
       <c r="O55">
-        <v>218.7250770959999</v>
+        <v>217.805738928</v>
       </c>
       <c r="P55">
-        <v>692.6294108039998</v>
+        <v>689.7181732719998</v>
       </c>
       <c r="Q55">
-        <v>1446.129410804</v>
+        <v>1443.218173272</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1344533073008188</v>
+        <v>0.1361314773469627</v>
       </c>
       <c r="T55">
-        <v>1.822805307327497</v>
+        <v>1.857310249780793</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.488977386930745</v>
+        <v>5.387329657543139</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08531559957960283</v>
+        <v>0.08516330472782084</v>
       </c>
       <c r="C56">
-        <v>3241.37533888419</v>
+        <v>3197.625196973837</v>
       </c>
       <c r="D56">
-        <v>6595.801338884189</v>
+        <v>6621.320196973837</v>
       </c>
       <c r="E56">
-        <v>67.22599999999966</v>
+        <v>136.4949999999999</v>
       </c>
       <c r="F56">
-        <v>3740.526</v>
+        <v>3809.795</v>
       </c>
       <c r="G56">
         <v>386.1</v>
@@ -5885,28 +5885,28 @@
         <v>1114.375</v>
       </c>
       <c r="M56">
-        <v>206.8510878</v>
+        <v>210.6816635</v>
       </c>
       <c r="N56">
-        <v>907.5239121999998</v>
+        <v>903.6933364999998</v>
       </c>
       <c r="O56">
-        <v>217.805738928</v>
+        <v>216.8864007599999</v>
       </c>
       <c r="P56">
-        <v>689.7181732719998</v>
+        <v>686.8069357399999</v>
       </c>
       <c r="Q56">
-        <v>1443.218173272</v>
+        <v>1440.30693574</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1361314773469627</v>
+        <v>0.1378842327284908</v>
       </c>
       <c r="T56">
-        <v>1.857310249780793</v>
+        <v>1.893348745232013</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.387329657543139</v>
+        <v>5.289378209224172</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08516330472782084</v>
+        <v>0.08501100987603884</v>
       </c>
       <c r="C57">
-        <v>3197.625196973837</v>
+        <v>3154.073284628229</v>
       </c>
       <c r="D57">
-        <v>6621.320196973837</v>
+        <v>6647.037284628229</v>
       </c>
       <c r="E57">
-        <v>136.4949999999999</v>
+        <v>205.7640000000001</v>
       </c>
       <c r="F57">
-        <v>3809.795</v>
+        <v>3879.064</v>
       </c>
       <c r="G57">
         <v>386.1</v>
@@ -5967,28 +5967,28 @@
         <v>1114.375</v>
       </c>
       <c r="M57">
-        <v>210.6816635</v>
+        <v>214.5122392</v>
       </c>
       <c r="N57">
-        <v>903.6933364999998</v>
+        <v>899.8627607999997</v>
       </c>
       <c r="O57">
-        <v>216.8864007599999</v>
+        <v>215.9670625919999</v>
       </c>
       <c r="P57">
-        <v>686.8069357399999</v>
+        <v>683.8956982079998</v>
       </c>
       <c r="Q57">
-        <v>1440.30693574</v>
+        <v>1437.395698208</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1378842327284908</v>
+        <v>0.1397166588091792</v>
       </c>
       <c r="T57">
-        <v>1.893348745232013</v>
+        <v>1.931025354112834</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.289378209224172</v>
+        <v>5.194925026916597</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08501100987603884</v>
+        <v>0.08485871502425685</v>
       </c>
       <c r="C58">
-        <v>3154.073284628229</v>
+        <v>3110.721920613517</v>
       </c>
       <c r="D58">
-        <v>6647.037284628229</v>
+        <v>6672.954920613517</v>
       </c>
       <c r="E58">
-        <v>205.7640000000001</v>
+        <v>275.0329999999999</v>
       </c>
       <c r="F58">
-        <v>3879.064</v>
+        <v>3948.333</v>
       </c>
       <c r="G58">
         <v>386.1</v>
@@ -6049,28 +6049,28 @@
         <v>1114.375</v>
       </c>
       <c r="M58">
-        <v>214.5122392</v>
+        <v>218.3428149</v>
       </c>
       <c r="N58">
-        <v>899.8627607999997</v>
+        <v>896.0321850999998</v>
       </c>
       <c r="O58">
-        <v>215.9670625919999</v>
+        <v>215.0477244239999</v>
       </c>
       <c r="P58">
-        <v>683.8956982079998</v>
+        <v>680.9844606759998</v>
       </c>
       <c r="Q58">
-        <v>1437.395698208</v>
+        <v>1434.484460676</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1397166588091792</v>
+        <v>0.1416343140098997</v>
       </c>
       <c r="T58">
-        <v>1.931025354112834</v>
+        <v>1.970454363406718</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.194925026916597</v>
+        <v>5.103785991356657</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08485871502425685</v>
+        <v>0.08470642017247486</v>
       </c>
       <c r="C59">
-        <v>3110.721920613517</v>
+        <v>3067.573460002069</v>
       </c>
       <c r="D59">
-        <v>6672.954920613517</v>
+        <v>6699.075460002069</v>
       </c>
       <c r="E59">
-        <v>275.0329999999999</v>
+        <v>344.3020000000001</v>
       </c>
       <c r="F59">
-        <v>3948.333</v>
+        <v>4017.602</v>
       </c>
       <c r="G59">
         <v>386.1</v>
@@ -6131,28 +6131,28 @@
         <v>1114.375</v>
       </c>
       <c r="M59">
-        <v>218.3428149</v>
+        <v>222.1733906</v>
       </c>
       <c r="N59">
-        <v>896.0321850999998</v>
+        <v>892.2016093999997</v>
       </c>
       <c r="O59">
-        <v>215.0477244239999</v>
+        <v>214.1283862559999</v>
       </c>
       <c r="P59">
-        <v>680.9844606759998</v>
+        <v>678.0732231439998</v>
       </c>
       <c r="Q59">
-        <v>1434.484460676</v>
+        <v>1431.573223144</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1416343140098997</v>
+        <v>0.1436432861249402</v>
       </c>
       <c r="T59">
-        <v>1.970454363406718</v>
+        <v>2.011760944571737</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.103785991356657</v>
+        <v>5.015789681160853</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08470642017247487</v>
+        <v>0.08455412532069287</v>
       </c>
       <c r="C60">
-        <v>3067.573460002069</v>
+        <v>3024.630294885838</v>
       </c>
       <c r="D60">
-        <v>6699.075460002068</v>
+        <v>6725.401294885837</v>
       </c>
       <c r="E60">
-        <v>344.3019999999992</v>
+        <v>413.5709999999995</v>
       </c>
       <c r="F60">
-        <v>4017.601999999999</v>
+        <v>4086.871</v>
       </c>
       <c r="G60">
         <v>386.1</v>
@@ -6213,28 +6213,28 @@
         <v>1114.375</v>
       </c>
       <c r="M60">
-        <v>222.1733906</v>
+        <v>226.0039663</v>
       </c>
       <c r="N60">
-        <v>892.2016093999998</v>
+        <v>888.3710336999998</v>
       </c>
       <c r="O60">
-        <v>214.1283862559999</v>
+        <v>213.2090480879999</v>
       </c>
       <c r="P60">
-        <v>678.0732231439999</v>
+        <v>675.1619856119999</v>
       </c>
       <c r="Q60">
-        <v>1431.573223144</v>
+        <v>1428.661985612</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1436432861249402</v>
+        <v>0.1457502568797387</v>
       </c>
       <c r="T60">
-        <v>2.011760944571737</v>
+        <v>2.055082480915539</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.015789681160854</v>
+        <v>4.930776296734399</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08455412532069287</v>
+        <v>0.08440183046891088</v>
       </c>
       <c r="C61">
-        <v>3024.630294885838</v>
+        <v>2981.894855106615</v>
       </c>
       <c r="D61">
-        <v>6725.401294885837</v>
+        <v>6751.934855106614</v>
       </c>
       <c r="E61">
-        <v>413.5709999999995</v>
+        <v>482.8399999999992</v>
       </c>
       <c r="F61">
-        <v>4086.871</v>
+        <v>4156.139999999999</v>
       </c>
       <c r="G61">
         <v>386.1</v>
@@ -6295,28 +6295,28 @@
         <v>1114.375</v>
       </c>
       <c r="M61">
-        <v>226.0039663</v>
+        <v>229.834542</v>
       </c>
       <c r="N61">
-        <v>888.3710336999998</v>
+        <v>884.5404579999998</v>
       </c>
       <c r="O61">
-        <v>213.2090480879999</v>
+        <v>212.28970992</v>
       </c>
       <c r="P61">
-        <v>675.1619856119999</v>
+        <v>672.2507480799999</v>
       </c>
       <c r="Q61">
-        <v>1428.661985612</v>
+        <v>1425.75074808</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1457502568797387</v>
+        <v>0.1479625761722772</v>
       </c>
       <c r="T61">
-        <v>2.055082480915539</v>
+        <v>2.10057009407653</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.930776296734399</v>
+        <v>4.848596691788826</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08440183046891088</v>
+        <v>0.08424953561712889</v>
       </c>
       <c r="C62">
-        <v>2981.894855106615</v>
+        <v>2939.369609003657</v>
       </c>
       <c r="D62">
-        <v>6751.934855106614</v>
+        <v>6778.678609003657</v>
       </c>
       <c r="E62">
-        <v>482.8399999999992</v>
+        <v>552.1089999999995</v>
       </c>
       <c r="F62">
-        <v>4156.139999999999</v>
+        <v>4225.409</v>
       </c>
       <c r="G62">
         <v>386.1</v>
@@ -6377,28 +6377,28 @@
         <v>1114.375</v>
       </c>
       <c r="M62">
-        <v>229.834542</v>
+        <v>233.6651177</v>
       </c>
       <c r="N62">
-        <v>884.5404579999998</v>
+        <v>880.7098822999998</v>
       </c>
       <c r="O62">
-        <v>212.28970992</v>
+        <v>211.3703717519999</v>
       </c>
       <c r="P62">
-        <v>672.2507480799999</v>
+        <v>669.3395105479999</v>
       </c>
       <c r="Q62">
-        <v>1425.75074808</v>
+        <v>1422.839510548</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1479625761722772</v>
+        <v>0.1502883477362279</v>
       </c>
       <c r="T62">
-        <v>2.10057009407653</v>
+        <v>2.148390405348342</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.848596691788826</v>
+        <v>4.769111500120156</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08424953561712889</v>
+        <v>0.0840972407653469</v>
       </c>
       <c r="C63">
-        <v>2939.369609003657</v>
+        <v>2897.057064179146</v>
       </c>
       <c r="D63">
-        <v>6778.678609003657</v>
+        <v>6805.635064179145</v>
       </c>
       <c r="E63">
-        <v>552.1089999999995</v>
+        <v>621.3779999999997</v>
       </c>
       <c r="F63">
-        <v>4225.409</v>
+        <v>4294.678</v>
       </c>
       <c r="G63">
         <v>386.1</v>
@@ -6459,28 +6459,28 @@
         <v>1114.375</v>
       </c>
       <c r="M63">
-        <v>233.6651177</v>
+        <v>237.4956934</v>
       </c>
       <c r="N63">
-        <v>880.7098822999998</v>
+        <v>876.8793065999998</v>
       </c>
       <c r="O63">
-        <v>211.3703717519999</v>
+        <v>210.451033584</v>
       </c>
       <c r="P63">
-        <v>669.3395105479999</v>
+        <v>666.4282730159998</v>
       </c>
       <c r="Q63">
-        <v>1422.839510548</v>
+        <v>1419.928273016</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1502883477362279</v>
+        <v>0.1527365283298603</v>
       </c>
       <c r="T63">
-        <v>2.148390405348342</v>
+        <v>2.198727575108145</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.769111500120156</v>
+        <v>4.692190346892412</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0840972407653469</v>
+        <v>0.08394494591356488</v>
       </c>
       <c r="C64">
-        <v>2897.057064179146</v>
+        <v>2854.95976828197</v>
       </c>
       <c r="D64">
-        <v>6805.635064179145</v>
+        <v>6832.80676828197</v>
       </c>
       <c r="E64">
-        <v>621.3779999999997</v>
+        <v>690.6469999999999</v>
       </c>
       <c r="F64">
-        <v>4294.678</v>
+        <v>4363.947</v>
       </c>
       <c r="G64">
         <v>386.1</v>
@@ -6541,28 +6541,28 @@
         <v>1114.375</v>
       </c>
       <c r="M64">
-        <v>237.4956934</v>
+        <v>241.3262691</v>
       </c>
       <c r="N64">
-        <v>876.8793065999998</v>
+        <v>873.0487308999998</v>
       </c>
       <c r="O64">
-        <v>210.451033584</v>
+        <v>209.5316954159999</v>
       </c>
       <c r="P64">
-        <v>666.4282730159998</v>
+        <v>663.5170354839998</v>
       </c>
       <c r="Q64">
-        <v>1419.928273016</v>
+        <v>1417.017035484</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1527365283298603</v>
+        <v>0.1553170430096348</v>
       </c>
       <c r="T64">
-        <v>2.198727575108145</v>
+        <v>2.25178567296307</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.692190346892412</v>
+        <v>4.617711135036976</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08394494591356488</v>
+        <v>0.08379265106178291</v>
       </c>
       <c r="C65">
-        <v>2854.95976828197</v>
+        <v>2813.080309810363</v>
       </c>
       <c r="D65">
-        <v>6832.80676828197</v>
+        <v>6860.196309810362</v>
       </c>
       <c r="E65">
-        <v>690.6469999999999</v>
+        <v>759.9159999999993</v>
       </c>
       <c r="F65">
-        <v>4363.947</v>
+        <v>4433.215999999999</v>
       </c>
       <c r="G65">
         <v>386.1</v>
@@ -6623,28 +6623,28 @@
         <v>1114.375</v>
       </c>
       <c r="M65">
-        <v>241.3262691</v>
+        <v>245.1568448</v>
       </c>
       <c r="N65">
-        <v>873.0487308999998</v>
+        <v>869.2181551999997</v>
       </c>
       <c r="O65">
-        <v>209.5316954159999</v>
+        <v>208.6123572479999</v>
       </c>
       <c r="P65">
-        <v>663.5170354839998</v>
+        <v>660.6057979519998</v>
       </c>
       <c r="Q65">
-        <v>1417.017035484</v>
+        <v>1414.105797952</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1553170430096348</v>
+        <v>0.1580409196160636</v>
       </c>
       <c r="T65">
-        <v>2.25178567296307</v>
+        <v>2.307791442921048</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.617711135036976</v>
+        <v>4.545559398552023</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08379265106178291</v>
+        <v>0.08487535621000092</v>
       </c>
       <c r="C66">
-        <v>2813.080309810363</v>
+        <v>2553.728081329981</v>
       </c>
       <c r="D66">
-        <v>6860.196309810362</v>
+        <v>6670.113081329981</v>
       </c>
       <c r="E66">
-        <v>759.9159999999993</v>
+        <v>829.1849999999995</v>
       </c>
       <c r="F66">
-        <v>4433.215999999999</v>
+        <v>4502.485</v>
       </c>
       <c r="G66">
         <v>386.1</v>
@@ -6705,45 +6705,45 @@
         <v>1114.375</v>
       </c>
       <c r="M66">
-        <v>245.1568448</v>
+        <v>260.243633</v>
       </c>
       <c r="N66">
-        <v>869.2181551999997</v>
+        <v>854.1313669999997</v>
       </c>
       <c r="O66">
-        <v>208.6123572479999</v>
+        <v>204.9915280799999</v>
       </c>
       <c r="P66">
-        <v>660.6057979519998</v>
+        <v>649.1398389199998</v>
       </c>
       <c r="Q66">
-        <v>1414.105797952</v>
+        <v>1402.63983892</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1580409196160636</v>
+        <v>0.1609204463142883</v>
       </c>
       <c r="T66">
-        <v>2.307791442921048</v>
+        <v>2.366997542590911</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.545559398552023</v>
+        <v>4.282045201851297</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08487535621000092</v>
+        <v>0.08474206135821892</v>
       </c>
       <c r="C67">
-        <v>2553.728081329981</v>
+        <v>2507.290223378845</v>
       </c>
       <c r="D67">
-        <v>6670.113081329981</v>
+        <v>6692.944223378844</v>
       </c>
       <c r="E67">
-        <v>829.1849999999995</v>
+        <v>898.4539999999997</v>
       </c>
       <c r="F67">
-        <v>4502.485</v>
+        <v>4571.754</v>
       </c>
       <c r="G67">
         <v>386.1</v>
@@ -6787,28 +6787,28 @@
         <v>1114.375</v>
       </c>
       <c r="M67">
-        <v>260.243633</v>
+        <v>264.2473812</v>
       </c>
       <c r="N67">
-        <v>854.1313669999997</v>
+        <v>850.1276187999997</v>
       </c>
       <c r="O67">
-        <v>204.9915280799999</v>
+        <v>204.0306285119999</v>
       </c>
       <c r="P67">
-        <v>649.1398389199998</v>
+        <v>646.0969902879998</v>
       </c>
       <c r="Q67">
-        <v>1402.63983892</v>
+        <v>1399.596990288</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1609204463142883</v>
+        <v>0.163969356935938</v>
       </c>
       <c r="T67">
-        <v>2.366997542590911</v>
+        <v>2.429686354006059</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.282045201851297</v>
+        <v>4.217165729095974</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08474206135821892</v>
+        <v>0.08460876650643692</v>
       </c>
       <c r="C68">
-        <v>2507.290223378845</v>
+        <v>2461.009199770532</v>
       </c>
       <c r="D68">
-        <v>6692.944223378844</v>
+        <v>6715.932199770532</v>
       </c>
       <c r="E68">
-        <v>898.4539999999997</v>
+        <v>967.723</v>
       </c>
       <c r="F68">
-        <v>4571.754</v>
+        <v>4641.023</v>
       </c>
       <c r="G68">
         <v>386.1</v>
@@ -6869,28 +6869,28 @@
         <v>1114.375</v>
       </c>
       <c r="M68">
-        <v>264.2473812</v>
+        <v>268.2511294</v>
       </c>
       <c r="N68">
-        <v>850.1276187999997</v>
+        <v>846.1238705999997</v>
       </c>
       <c r="O68">
-        <v>204.0306285119999</v>
+        <v>203.0697289439999</v>
       </c>
       <c r="P68">
-        <v>646.0969902879998</v>
+        <v>643.0541416559997</v>
       </c>
       <c r="Q68">
-        <v>1399.596990288</v>
+        <v>1396.554141656</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.163969356935938</v>
+        <v>0.1672030500195058</v>
       </c>
       <c r="T68">
-        <v>2.429686354006059</v>
+        <v>2.496174487325155</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.217165729095974</v>
+        <v>4.154222957019915</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08460876650643692</v>
+        <v>0.08447547165465494</v>
       </c>
       <c r="C69">
-        <v>2461.009199770532</v>
+        <v>2414.886632091766</v>
       </c>
       <c r="D69">
-        <v>6715.932199770532</v>
+        <v>6739.078632091766</v>
       </c>
       <c r="E69">
-        <v>967.723</v>
+        <v>1036.992</v>
       </c>
       <c r="F69">
-        <v>4641.023</v>
+        <v>4710.292</v>
       </c>
       <c r="G69">
         <v>386.1</v>
@@ -6951,28 +6951,28 @@
         <v>1114.375</v>
       </c>
       <c r="M69">
-        <v>268.2511294</v>
+        <v>272.2548776</v>
       </c>
       <c r="N69">
-        <v>846.1238705999997</v>
+        <v>842.1201223999997</v>
       </c>
       <c r="O69">
-        <v>203.0697289439999</v>
+        <v>202.1088293759999</v>
       </c>
       <c r="P69">
-        <v>643.0541416559997</v>
+        <v>640.0112930239998</v>
       </c>
       <c r="Q69">
-        <v>1396.554141656</v>
+        <v>1393.511293024</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1672030500195058</v>
+        <v>0.1706388489207967</v>
       </c>
       <c r="T69">
-        <v>2.496174487325155</v>
+        <v>2.566818128976695</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.154222957019915</v>
+        <v>4.093131442946092</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08447547165465494</v>
+        <v>0.08434217680287294</v>
       </c>
       <c r="C70">
-        <v>2414.886632091766</v>
+        <v>2368.924164361759</v>
       </c>
       <c r="D70">
-        <v>6739.078632091766</v>
+        <v>6762.385164361758</v>
       </c>
       <c r="E70">
-        <v>1036.992</v>
+        <v>1106.261</v>
       </c>
       <c r="F70">
-        <v>4710.292</v>
+        <v>4779.561</v>
       </c>
       <c r="G70">
         <v>386.1</v>
@@ -7033,28 +7033,28 @@
         <v>1114.375</v>
       </c>
       <c r="M70">
-        <v>272.2548776</v>
+        <v>276.2586258</v>
       </c>
       <c r="N70">
-        <v>842.1201223999997</v>
+        <v>838.1163741999998</v>
       </c>
       <c r="O70">
-        <v>202.1088293759999</v>
+        <v>201.1479298079999</v>
       </c>
       <c r="P70">
-        <v>640.0112930239998</v>
+        <v>636.9684443919998</v>
       </c>
       <c r="Q70">
-        <v>1393.511293024</v>
+        <v>1390.468444392</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1706388489207967</v>
+        <v>0.1742963122673321</v>
       </c>
       <c r="T70">
-        <v>2.566818128976695</v>
+        <v>2.642019424928335</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.093131442946092</v>
+        <v>4.033810697396149</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08434217680287294</v>
+        <v>0.08607088195109094</v>
       </c>
       <c r="C71">
-        <v>2368.924164361759</v>
+        <v>2009.366760396258</v>
       </c>
       <c r="D71">
-        <v>6762.385164361758</v>
+        <v>6472.096760396257</v>
       </c>
       <c r="E71">
-        <v>1106.261</v>
+        <v>1175.53</v>
       </c>
       <c r="F71">
-        <v>4779.561</v>
+        <v>4848.83</v>
       </c>
       <c r="G71">
         <v>386.1</v>
@@ -7115,45 +7115,45 @@
         <v>1114.375</v>
       </c>
       <c r="M71">
-        <v>276.2586258</v>
+        <v>297.233279</v>
       </c>
       <c r="N71">
-        <v>838.1163741999998</v>
+        <v>817.1417209999997</v>
       </c>
       <c r="O71">
-        <v>201.1479298079999</v>
+        <v>196.1140130399999</v>
       </c>
       <c r="P71">
-        <v>636.9684443919998</v>
+        <v>621.0277079599998</v>
       </c>
       <c r="Q71">
-        <v>1390.468444392</v>
+        <v>1374.52770796</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1742963122673321</v>
+        <v>0.1781976065036365</v>
       </c>
       <c r="T71">
-        <v>2.642019424928335</v>
+        <v>2.722234140610084</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.24</v>
       </c>
       <c r="W71">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.033810697396149</v>
+        <v>3.749159595282061</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08607088195109094</v>
+        <v>0.08596418709930895</v>
       </c>
       <c r="C72">
-        <v>2009.366760396258</v>
+        <v>1957.290674144563</v>
       </c>
       <c r="D72">
-        <v>6472.096760396257</v>
+        <v>6489.289674144563</v>
       </c>
       <c r="E72">
-        <v>1175.53</v>
+        <v>1244.799</v>
       </c>
       <c r="F72">
-        <v>4848.83</v>
+        <v>4918.099</v>
       </c>
       <c r="G72">
         <v>386.1</v>
@@ -7197,28 +7197,28 @@
         <v>1114.375</v>
       </c>
       <c r="M72">
-        <v>297.233279</v>
+        <v>301.4794687</v>
       </c>
       <c r="N72">
-        <v>817.1417209999997</v>
+        <v>812.8955312999998</v>
       </c>
       <c r="O72">
-        <v>196.1140130399999</v>
+        <v>195.0949275119999</v>
       </c>
       <c r="P72">
-        <v>621.0277079599998</v>
+        <v>617.8006037879999</v>
       </c>
       <c r="Q72">
-        <v>1374.52770796</v>
+        <v>1371.300603788</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1781976065036365</v>
+        <v>0.1823679555148585</v>
       </c>
       <c r="T72">
-        <v>2.722234140610084</v>
+        <v>2.807980905649195</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.749159595282061</v>
+        <v>3.696354530559778</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08596418709930896</v>
+        <v>0.08585749224752695</v>
       </c>
       <c r="C73">
-        <v>1957.290674144562</v>
+        <v>1905.306176021889</v>
       </c>
       <c r="D73">
-        <v>6489.289674144561</v>
+        <v>6506.574176021888</v>
       </c>
       <c r="E73">
-        <v>1244.798999999999</v>
+        <v>1314.067999999999</v>
       </c>
       <c r="F73">
-        <v>4918.098999999999</v>
+        <v>4987.367999999999</v>
       </c>
       <c r="G73">
         <v>386.1</v>
@@ -7279,28 +7279,28 @@
         <v>1114.375</v>
       </c>
       <c r="M73">
-        <v>301.4794687</v>
+        <v>305.7256584</v>
       </c>
       <c r="N73">
-        <v>812.8955312999998</v>
+        <v>808.6493415999998</v>
       </c>
       <c r="O73">
-        <v>195.0949275119999</v>
+        <v>194.075841984</v>
       </c>
       <c r="P73">
-        <v>617.8006037879999</v>
+        <v>614.5734996159999</v>
       </c>
       <c r="Q73">
-        <v>1371.300603788</v>
+        <v>1368.073499616</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1823679555148585</v>
+        <v>0.1868361865983106</v>
       </c>
       <c r="T73">
-        <v>2.807980905649194</v>
+        <v>2.89985243961967</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.696354530559778</v>
+        <v>3.645016273190893</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08585749224752695</v>
+        <v>0.08575079739574495</v>
       </c>
       <c r="C74">
-        <v>1905.306176021889</v>
+        <v>1853.413999829494</v>
       </c>
       <c r="D74">
-        <v>6506.574176021888</v>
+        <v>6523.950999829493</v>
       </c>
       <c r="E74">
-        <v>1314.067999999999</v>
+        <v>1383.337</v>
       </c>
       <c r="F74">
-        <v>4987.367999999999</v>
+        <v>5056.637</v>
       </c>
       <c r="G74">
         <v>386.1</v>
@@ -7361,28 +7361,28 @@
         <v>1114.375</v>
       </c>
       <c r="M74">
-        <v>305.7256584</v>
+        <v>309.9718481</v>
       </c>
       <c r="N74">
-        <v>808.6493415999998</v>
+        <v>804.4031518999998</v>
       </c>
       <c r="O74">
-        <v>194.075841984</v>
+        <v>193.0567564559999</v>
       </c>
       <c r="P74">
-        <v>614.5734996159999</v>
+        <v>611.3463954439999</v>
       </c>
       <c r="Q74">
-        <v>1368.073499616</v>
+        <v>1364.846395444</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1868361865983106</v>
+        <v>0.1916353977620184</v>
       </c>
       <c r="T74">
-        <v>2.89985243961967</v>
+        <v>2.998529272402773</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.645016273190893</v>
+        <v>3.595084543421154</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08575079739574495</v>
+        <v>0.08564410254396296</v>
       </c>
       <c r="C75">
-        <v>1853.413999829494</v>
+        <v>1801.614887228559</v>
       </c>
       <c r="D75">
-        <v>6523.950999829493</v>
+        <v>6541.420887228559</v>
       </c>
       <c r="E75">
-        <v>1383.337</v>
+        <v>1452.606</v>
       </c>
       <c r="F75">
-        <v>5056.637</v>
+        <v>5125.906</v>
       </c>
       <c r="G75">
         <v>386.1</v>
@@ -7443,28 +7443,28 @@
         <v>1114.375</v>
       </c>
       <c r="M75">
-        <v>309.9718481</v>
+        <v>314.2180378</v>
       </c>
       <c r="N75">
-        <v>804.4031518999998</v>
+        <v>800.1569621999997</v>
       </c>
       <c r="O75">
-        <v>193.0567564559999</v>
+        <v>192.0376709279999</v>
       </c>
       <c r="P75">
-        <v>611.3463954439999</v>
+        <v>608.1192912719998</v>
       </c>
       <c r="Q75">
-        <v>1364.846395444</v>
+        <v>1361.619291272</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1916353977620184</v>
+        <v>0.1968037790152422</v>
       </c>
       <c r="T75">
-        <v>2.998529272402773</v>
+        <v>3.104796630784577</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.595084543421154</v>
+        <v>3.546502319861408</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08564410254396296</v>
+        <v>0.08713340769218098</v>
       </c>
       <c r="C76">
-        <v>1801.614887228559</v>
+        <v>1496.648606313265</v>
       </c>
       <c r="D76">
-        <v>6541.420887228559</v>
+        <v>6305.723606313264</v>
       </c>
       <c r="E76">
-        <v>1452.606</v>
+        <v>1521.874999999999</v>
       </c>
       <c r="F76">
-        <v>5125.906</v>
+        <v>5195.174999999999</v>
       </c>
       <c r="G76">
         <v>386.1</v>
@@ -7525,45 +7525,45 @@
         <v>1114.375</v>
       </c>
       <c r="M76">
-        <v>314.2180378</v>
+        <v>333.0107175</v>
       </c>
       <c r="N76">
-        <v>800.1569621999997</v>
+        <v>781.3642824999997</v>
       </c>
       <c r="O76">
-        <v>192.0376709279999</v>
+        <v>187.5274277999999</v>
       </c>
       <c r="P76">
-        <v>608.1192912719998</v>
+        <v>593.8368546999998</v>
       </c>
       <c r="Q76">
-        <v>1361.619291272</v>
+        <v>1347.3368547</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1968037790152422</v>
+        <v>0.2023856307687239</v>
       </c>
       <c r="T76">
-        <v>3.104796630784577</v>
+        <v>3.219565377836926</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.24</v>
       </c>
       <c r="W76">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.546502319861408</v>
+        <v>3.346363769808699</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08713340769218098</v>
+        <v>0.08704799284039899</v>
       </c>
       <c r="C77">
-        <v>1496.648606313265</v>
+        <v>1440.437270701819</v>
       </c>
       <c r="D77">
-        <v>6305.723606313264</v>
+        <v>6318.781270701818</v>
       </c>
       <c r="E77">
-        <v>1521.874999999999</v>
+        <v>1591.143999999999</v>
       </c>
       <c r="F77">
-        <v>5195.174999999999</v>
+        <v>5264.444</v>
       </c>
       <c r="G77">
         <v>386.1</v>
@@ -7607,28 +7607,28 @@
         <v>1114.375</v>
       </c>
       <c r="M77">
-        <v>333.0107175</v>
+        <v>337.4508604</v>
       </c>
       <c r="N77">
-        <v>781.3642824999997</v>
+        <v>776.9241395999998</v>
       </c>
       <c r="O77">
-        <v>187.5274277999999</v>
+        <v>186.4617935039999</v>
       </c>
       <c r="P77">
-        <v>593.8368546999998</v>
+        <v>590.4623460959998</v>
       </c>
       <c r="Q77">
-        <v>1347.3368547</v>
+        <v>1343.962346096</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2023856307687239</v>
+        <v>0.2084326368349958</v>
       </c>
       <c r="T77">
-        <v>3.219565377836926</v>
+        <v>3.343898187143636</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.346363769808699</v>
+        <v>3.302332667574374</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08704799284039899</v>
+        <v>0.08696257798861699</v>
       </c>
       <c r="C78">
-        <v>1440.437270701819</v>
+        <v>1384.280125985254</v>
       </c>
       <c r="D78">
-        <v>6318.781270701818</v>
+        <v>6331.893125985253</v>
       </c>
       <c r="E78">
-        <v>1591.143999999999</v>
+        <v>1660.413</v>
       </c>
       <c r="F78">
-        <v>5264.444</v>
+        <v>5333.713</v>
       </c>
       <c r="G78">
         <v>386.1</v>
@@ -7689,28 +7689,28 @@
         <v>1114.375</v>
       </c>
       <c r="M78">
-        <v>337.4508604</v>
+        <v>341.8910033</v>
       </c>
       <c r="N78">
-        <v>776.9241395999998</v>
+        <v>772.4839966999998</v>
       </c>
       <c r="O78">
-        <v>186.4617935039999</v>
+        <v>185.3961592079999</v>
       </c>
       <c r="P78">
-        <v>590.4623460959998</v>
+        <v>587.0878374919998</v>
       </c>
       <c r="Q78">
-        <v>1343.962346096</v>
+        <v>1340.587837492</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2084326368349958</v>
+        <v>0.2150054695157261</v>
       </c>
       <c r="T78">
-        <v>3.343898187143636</v>
+        <v>3.479042545085713</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.302332667574374</v>
+        <v>3.259445230333148</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08696257798861699</v>
+        <v>0.086877163136835</v>
       </c>
       <c r="C79">
-        <v>1384.280125985254</v>
+        <v>1328.177510213245</v>
       </c>
       <c r="D79">
-        <v>6331.893125985253</v>
+        <v>6345.059510213245</v>
       </c>
       <c r="E79">
-        <v>1660.413</v>
+        <v>1729.682</v>
       </c>
       <c r="F79">
-        <v>5333.713</v>
+        <v>5402.982</v>
       </c>
       <c r="G79">
         <v>386.1</v>
@@ -7771,28 +7771,28 @@
         <v>1114.375</v>
       </c>
       <c r="M79">
-        <v>341.8910033</v>
+        <v>346.3311462</v>
       </c>
       <c r="N79">
-        <v>772.4839966999998</v>
+        <v>768.0438537999997</v>
       </c>
       <c r="O79">
-        <v>185.3961592079999</v>
+        <v>184.3305249119999</v>
       </c>
       <c r="P79">
-        <v>587.0878374919998</v>
+        <v>583.7133288879998</v>
       </c>
       <c r="Q79">
-        <v>1340.587837492</v>
+        <v>1337.213328888</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2150054695157261</v>
+        <v>0.2221758324401591</v>
       </c>
       <c r="T79">
-        <v>3.479042545085713</v>
+        <v>3.626472753749796</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.259445230333148</v>
+        <v>3.217657470969903</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.086877163136835</v>
+        <v>0.08679174828505301</v>
       </c>
       <c r="C80">
-        <v>1328.177510213245</v>
+        <v>1272.129764253058</v>
       </c>
       <c r="D80">
-        <v>6345.059510213245</v>
+        <v>6358.280764253058</v>
       </c>
       <c r="E80">
-        <v>1729.682</v>
+        <v>1798.951</v>
       </c>
       <c r="F80">
-        <v>5402.982</v>
+        <v>5472.251</v>
       </c>
       <c r="G80">
         <v>386.1</v>
@@ -7853,28 +7853,28 @@
         <v>1114.375</v>
       </c>
       <c r="M80">
-        <v>346.3311462</v>
+        <v>350.7712891</v>
       </c>
       <c r="N80">
-        <v>768.0438537999997</v>
+        <v>763.6037108999997</v>
       </c>
       <c r="O80">
-        <v>184.3305249119999</v>
+        <v>183.2648906159999</v>
       </c>
       <c r="P80">
-        <v>583.7133288879998</v>
+        <v>580.3388202839998</v>
       </c>
       <c r="Q80">
-        <v>1337.213328888</v>
+        <v>1333.838820284</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2221758324401591</v>
+        <v>0.230029087071681</v>
       </c>
       <c r="T80">
-        <v>3.626472753749796</v>
+        <v>3.787943934667603</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.217657470969903</v>
+        <v>3.17692762956522</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08679174828505301</v>
+        <v>0.08670633343327101</v>
       </c>
       <c r="C81">
-        <v>1272.129764253058</v>
+        <v>1216.137231818965</v>
       </c>
       <c r="D81">
-        <v>6358.280764253058</v>
+        <v>6371.557231818965</v>
       </c>
       <c r="E81">
-        <v>1798.951</v>
+        <v>1868.22</v>
       </c>
       <c r="F81">
-        <v>5472.251</v>
+        <v>5541.52</v>
       </c>
       <c r="G81">
         <v>386.1</v>
@@ -7935,28 +7935,28 @@
         <v>1114.375</v>
       </c>
       <c r="M81">
-        <v>350.7712891</v>
+        <v>355.2114320000001</v>
       </c>
       <c r="N81">
-        <v>763.6037108999997</v>
+        <v>759.1635679999997</v>
       </c>
       <c r="O81">
-        <v>183.2648906159999</v>
+        <v>182.1992563199999</v>
       </c>
       <c r="P81">
-        <v>580.3388202839998</v>
+        <v>576.9643116799998</v>
       </c>
       <c r="Q81">
-        <v>1333.838820284</v>
+        <v>1330.46431168</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.230029087071681</v>
+        <v>0.2386676671663551</v>
       </c>
       <c r="T81">
-        <v>3.787943934667603</v>
+        <v>3.965562233677189</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.17692762956522</v>
+        <v>3.137216034195655</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08670633343327101</v>
+        <v>0.08662091858148901</v>
       </c>
       <c r="C82">
-        <v>1216.137231818965</v>
+        <v>1160.200259502026</v>
       </c>
       <c r="D82">
-        <v>6371.557231818965</v>
+        <v>6384.889259502025</v>
       </c>
       <c r="E82">
-        <v>1868.22</v>
+        <v>1937.489</v>
       </c>
       <c r="F82">
-        <v>5541.52</v>
+        <v>5610.789</v>
       </c>
       <c r="G82">
         <v>386.1</v>
@@ -8017,28 +8017,28 @@
         <v>1114.375</v>
       </c>
       <c r="M82">
-        <v>355.2114320000001</v>
+        <v>359.6515749</v>
       </c>
       <c r="N82">
-        <v>759.1635679999997</v>
+        <v>754.7234250999998</v>
       </c>
       <c r="O82">
-        <v>182.1992563199999</v>
+        <v>181.1336220239999</v>
       </c>
       <c r="P82">
-        <v>576.9643116799998</v>
+        <v>573.5898030759998</v>
       </c>
       <c r="Q82">
-        <v>1330.46431168</v>
+        <v>1327.089803076</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2386676671663551</v>
+        <v>0.2482155714815212</v>
       </c>
       <c r="T82">
-        <v>3.965562233677189</v>
+        <v>4.161877195740417</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.137216034195655</v>
+        <v>3.098484972045092</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08662091858148901</v>
+        <v>0.08653550372970702</v>
       </c>
       <c r="C83">
-        <v>1160.200259502026</v>
+        <v>1104.319196800248</v>
       </c>
       <c r="D83">
-        <v>6384.889259502025</v>
+        <v>6398.277196800248</v>
       </c>
       <c r="E83">
-        <v>1937.489</v>
+        <v>2006.758</v>
       </c>
       <c r="F83">
-        <v>5610.789</v>
+        <v>5680.058</v>
       </c>
       <c r="G83">
         <v>386.1</v>
@@ -8099,28 +8099,28 @@
         <v>1114.375</v>
       </c>
       <c r="M83">
-        <v>359.6515749</v>
+        <v>364.0917178</v>
       </c>
       <c r="N83">
-        <v>754.7234250999998</v>
+        <v>750.2832821999998</v>
       </c>
       <c r="O83">
-        <v>181.1336220239999</v>
+        <v>180.0679877279999</v>
       </c>
       <c r="P83">
-        <v>573.5898030759998</v>
+        <v>570.2152944719999</v>
       </c>
       <c r="Q83">
-        <v>1327.089803076</v>
+        <v>1323.715294472</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2482155714815212</v>
+        <v>0.258824354053928</v>
       </c>
       <c r="T83">
-        <v>4.161877195740417</v>
+        <v>4.380004931366225</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.098484972045092</v>
+        <v>3.060698569946981</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08653550372970702</v>
+        <v>0.08645008887792505</v>
       </c>
       <c r="C84">
-        <v>1104.319196800248</v>
+        <v>1048.494396149131</v>
       </c>
       <c r="D84">
-        <v>6398.277196800248</v>
+        <v>6411.721396149131</v>
       </c>
       <c r="E84">
-        <v>2006.758</v>
+        <v>2076.027</v>
       </c>
       <c r="F84">
-        <v>5680.058</v>
+        <v>5749.327</v>
       </c>
       <c r="G84">
         <v>386.1</v>
@@ -8181,28 +8181,28 @@
         <v>1114.375</v>
       </c>
       <c r="M84">
-        <v>364.0917178</v>
+        <v>368.5318607</v>
       </c>
       <c r="N84">
-        <v>750.2832821999998</v>
+        <v>745.8431392999997</v>
       </c>
       <c r="O84">
-        <v>180.0679877279999</v>
+        <v>179.0023534319999</v>
       </c>
       <c r="P84">
-        <v>570.2152944719999</v>
+        <v>566.8407858679998</v>
       </c>
       <c r="Q84">
-        <v>1323.715294472</v>
+        <v>1320.340785868</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.258824354053928</v>
+        <v>0.2706812286936768</v>
       </c>
       <c r="T84">
-        <v>4.380004931366225</v>
+        <v>4.623794753536247</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.060698569946981</v>
+        <v>3.023822683562077</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08645008887792505</v>
+        <v>0.09134419402614305</v>
       </c>
       <c r="C85">
-        <v>1048.494396149131</v>
+        <v>290.2322244658071</v>
       </c>
       <c r="D85">
-        <v>6411.721396149131</v>
+        <v>5722.728224465807</v>
       </c>
       <c r="E85">
-        <v>2076.027</v>
+        <v>2145.296</v>
       </c>
       <c r="F85">
-        <v>5749.327</v>
+        <v>5818.596</v>
       </c>
       <c r="G85">
         <v>386.1</v>
@@ -8263,45 +8263,45 @@
         <v>1114.375</v>
       </c>
       <c r="M85">
-        <v>368.5318607</v>
+        <v>418.3570524</v>
       </c>
       <c r="N85">
-        <v>745.8431392999997</v>
+        <v>696.0179475999997</v>
       </c>
       <c r="O85">
-        <v>179.0023534319999</v>
+        <v>167.0443074239999</v>
       </c>
       <c r="P85">
-        <v>566.8407858679998</v>
+        <v>528.9736401759998</v>
       </c>
       <c r="Q85">
-        <v>1320.340785868</v>
+        <v>1282.473640176</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2706812286936768</v>
+        <v>0.2840202126633941</v>
       </c>
       <c r="T85">
-        <v>4.623794753536247</v>
+        <v>4.89805830347752</v>
       </c>
       <c r="U85">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V85">
         <v>0.24</v>
       </c>
       <c r="W85">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.023822683562077</v>
+        <v>2.663693592846434</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09134419402614305</v>
+        <v>0.09131805917436106</v>
       </c>
       <c r="C86">
-        <v>290.232224465808</v>
+        <v>224.2490116159606</v>
       </c>
       <c r="D86">
-        <v>5722.728224465807</v>
+        <v>5726.01401161596</v>
       </c>
       <c r="E86">
-        <v>2145.295999999999</v>
+        <v>2214.565</v>
       </c>
       <c r="F86">
-        <v>5818.596</v>
+        <v>5887.865</v>
       </c>
       <c r="G86">
         <v>386.1</v>
@@ -8345,28 +8345,28 @@
         <v>1114.375</v>
       </c>
       <c r="M86">
-        <v>418.3570524</v>
+        <v>423.3374935</v>
       </c>
       <c r="N86">
-        <v>696.0179475999998</v>
+        <v>691.0375064999998</v>
       </c>
       <c r="O86">
-        <v>167.044307424</v>
+        <v>165.8490015599999</v>
       </c>
       <c r="P86">
-        <v>528.9736401759999</v>
+        <v>525.1885049399999</v>
       </c>
       <c r="Q86">
-        <v>1282.473640176</v>
+        <v>1278.68850494</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2840202126633939</v>
+        <v>0.2991377278290737</v>
       </c>
       <c r="T86">
-        <v>4.898058303477517</v>
+        <v>5.208890326744294</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.663693592846434</v>
+        <v>2.632356021165887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09131805917436106</v>
+        <v>0.09129192432257907</v>
       </c>
       <c r="C87">
-        <v>224.2490116159606</v>
+        <v>158.2695740981726</v>
       </c>
       <c r="D87">
-        <v>5726.01401161596</v>
+        <v>5729.303574098172</v>
       </c>
       <c r="E87">
-        <v>2214.565</v>
+        <v>2283.834</v>
       </c>
       <c r="F87">
-        <v>5887.865</v>
+        <v>5957.134</v>
       </c>
       <c r="G87">
         <v>386.1</v>
@@ -8427,28 +8427,28 @@
         <v>1114.375</v>
       </c>
       <c r="M87">
-        <v>423.3374935</v>
+        <v>428.3179346000001</v>
       </c>
       <c r="N87">
-        <v>691.0375064999998</v>
+        <v>686.0570653999997</v>
       </c>
       <c r="O87">
-        <v>165.8490015599999</v>
+        <v>164.6536956959999</v>
       </c>
       <c r="P87">
-        <v>525.1885049399999</v>
+        <v>521.4033697039998</v>
       </c>
       <c r="Q87">
-        <v>1278.68850494</v>
+        <v>1274.903369704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2991377278290737</v>
+        <v>0.3164148880184218</v>
       </c>
       <c r="T87">
-        <v>5.208890326744294</v>
+        <v>5.564126924763467</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.632356021165887</v>
+        <v>2.601747230222098</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09129192432257907</v>
+        <v>0.09126578947079707</v>
       </c>
       <c r="C88">
-        <v>158.2695740981726</v>
+        <v>92.29391842290624</v>
       </c>
       <c r="D88">
-        <v>5729.303574098172</v>
+        <v>5732.596918422905</v>
       </c>
       <c r="E88">
-        <v>2283.834</v>
+        <v>2353.102999999999</v>
       </c>
       <c r="F88">
-        <v>5957.134</v>
+        <v>6026.402999999999</v>
       </c>
       <c r="G88">
         <v>386.1</v>
@@ -8509,28 +8509,28 @@
         <v>1114.375</v>
       </c>
       <c r="M88">
-        <v>428.3179346000001</v>
+        <v>433.2983757</v>
       </c>
       <c r="N88">
-        <v>686.0570653999997</v>
+        <v>681.0766242999998</v>
       </c>
       <c r="O88">
-        <v>164.6536956959999</v>
+        <v>163.4583898319999</v>
       </c>
       <c r="P88">
-        <v>521.4033697039998</v>
+        <v>517.6182344679999</v>
       </c>
       <c r="Q88">
-        <v>1274.903369704</v>
+        <v>1271.118234468</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3164148880184218</v>
+        <v>0.3363500728522851</v>
       </c>
       <c r="T88">
-        <v>5.564126924763467</v>
+        <v>5.974015307093282</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.601747230222098</v>
+        <v>2.571842089644833</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09126578947079707</v>
+        <v>0.09123965461901508</v>
       </c>
       <c r="C89">
-        <v>92.29391842290624</v>
+        <v>26.32205111559506</v>
       </c>
       <c r="D89">
-        <v>5732.596918422905</v>
+        <v>5735.894051115594</v>
       </c>
       <c r="E89">
-        <v>2353.102999999999</v>
+        <v>2422.371999999999</v>
       </c>
       <c r="F89">
-        <v>6026.402999999999</v>
+        <v>6095.672</v>
       </c>
       <c r="G89">
         <v>386.1</v>
@@ -8591,28 +8591,28 @@
         <v>1114.375</v>
       </c>
       <c r="M89">
-        <v>433.2983757</v>
+        <v>438.2788168</v>
       </c>
       <c r="N89">
-        <v>681.0766242999998</v>
+        <v>676.0961831999998</v>
       </c>
       <c r="O89">
-        <v>163.4583898319999</v>
+        <v>162.263083968</v>
       </c>
       <c r="P89">
-        <v>517.6182344679999</v>
+        <v>513.8330992319999</v>
       </c>
       <c r="Q89">
-        <v>1271.118234468</v>
+        <v>1267.333099232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3363500728522851</v>
+        <v>0.3596077884917923</v>
       </c>
       <c r="T89">
-        <v>5.974015307093282</v>
+        <v>6.4522184198114</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.571842089644833</v>
+        <v>2.542616611353414</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09123965461901508</v>
+        <v>0.09121351976723308</v>
       </c>
       <c r="C90">
-        <v>26.32205111559506</v>
+        <v>-39.64602128329534</v>
       </c>
       <c r="D90">
-        <v>5735.894051115594</v>
+        <v>5739.194978716704</v>
       </c>
       <c r="E90">
-        <v>2422.371999999999</v>
+        <v>2491.641</v>
       </c>
       <c r="F90">
-        <v>6095.672</v>
+        <v>6164.941</v>
       </c>
       <c r="G90">
         <v>386.1</v>
@@ -8673,28 +8673,28 @@
         <v>1114.375</v>
       </c>
       <c r="M90">
-        <v>438.2788168</v>
+        <v>443.2592579</v>
       </c>
       <c r="N90">
-        <v>676.0961831999998</v>
+        <v>671.1157420999998</v>
       </c>
       <c r="O90">
-        <v>162.263083968</v>
+        <v>161.067778104</v>
       </c>
       <c r="P90">
-        <v>513.8330992319999</v>
+        <v>510.0479639959999</v>
       </c>
       <c r="Q90">
-        <v>1267.333099232</v>
+        <v>1263.547963996</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3596077884917923</v>
+        <v>0.3870941797021189</v>
       </c>
       <c r="T90">
-        <v>6.4522184198114</v>
+        <v>7.01736755302372</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.542616611353414</v>
+        <v>2.514047885383151</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09121351976723308</v>
+        <v>0.09385498491545109</v>
       </c>
       <c r="C91">
-        <v>-39.64602128329534</v>
+        <v>-424.384551484598</v>
       </c>
       <c r="D91">
-        <v>5739.194978716704</v>
+        <v>5423.725448515402</v>
       </c>
       <c r="E91">
-        <v>2491.641</v>
+        <v>2560.91</v>
       </c>
       <c r="F91">
-        <v>6164.941</v>
+        <v>6234.21</v>
       </c>
       <c r="G91">
         <v>386.1</v>
@@ -8755,45 +8755,45 @@
         <v>1114.375</v>
       </c>
       <c r="M91">
-        <v>443.2592579</v>
+        <v>472.553118</v>
       </c>
       <c r="N91">
-        <v>671.1157420999998</v>
+        <v>641.8218819999997</v>
       </c>
       <c r="O91">
-        <v>161.067778104</v>
+        <v>154.0372516799999</v>
       </c>
       <c r="P91">
-        <v>510.0479639959999</v>
+        <v>487.7846303199998</v>
       </c>
       <c r="Q91">
-        <v>1263.547963996</v>
+        <v>1241.28463032</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3870941797021189</v>
+        <v>0.4200778491545109</v>
       </c>
       <c r="T91">
-        <v>7.01736755302372</v>
+        <v>7.695546512878506</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.24</v>
       </c>
       <c r="W91">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.514047885383151</v>
+        <v>2.358200501811099</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09385498491545109</v>
+        <v>0.09385849006366909</v>
       </c>
       <c r="C92">
-        <v>-424.384551484598</v>
+        <v>-494.0491311535725</v>
       </c>
       <c r="D92">
-        <v>5423.725448515402</v>
+        <v>5423.329868846427</v>
       </c>
       <c r="E92">
-        <v>2560.91</v>
+        <v>2630.179</v>
       </c>
       <c r="F92">
-        <v>6234.21</v>
+        <v>6303.479</v>
       </c>
       <c r="G92">
         <v>386.1</v>
@@ -8837,28 +8837,28 @@
         <v>1114.375</v>
       </c>
       <c r="M92">
-        <v>472.553118</v>
+        <v>477.8037082000001</v>
       </c>
       <c r="N92">
-        <v>641.8218819999997</v>
+        <v>636.5712917999997</v>
       </c>
       <c r="O92">
-        <v>154.0372516799999</v>
+        <v>152.7771100319999</v>
       </c>
       <c r="P92">
-        <v>487.7846303199998</v>
+        <v>483.7941817679998</v>
       </c>
       <c r="Q92">
-        <v>1241.28463032</v>
+        <v>1237.294181768</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4200778491545109</v>
+        <v>0.4603912229296567</v>
       </c>
       <c r="T92">
-        <v>7.695546512878506</v>
+        <v>8.524431908256577</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.358200501811099</v>
+        <v>2.332286210582406</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09385849006366909</v>
+        <v>0.09386199521188709</v>
       </c>
       <c r="C93">
-        <v>-494.0491311535725</v>
+        <v>-563.713653123511</v>
       </c>
       <c r="D93">
-        <v>5423.329868846427</v>
+        <v>5422.934346876488</v>
       </c>
       <c r="E93">
-        <v>2630.179</v>
+        <v>2699.447999999999</v>
       </c>
       <c r="F93">
-        <v>6303.479</v>
+        <v>6372.748</v>
       </c>
       <c r="G93">
         <v>386.1</v>
@@ -8919,28 +8919,28 @@
         <v>1114.375</v>
       </c>
       <c r="M93">
-        <v>477.8037082000001</v>
+        <v>483.0542984</v>
       </c>
       <c r="N93">
-        <v>636.5712917999997</v>
+        <v>631.3207015999998</v>
       </c>
       <c r="O93">
-        <v>152.7771100319999</v>
+        <v>151.5169683839999</v>
       </c>
       <c r="P93">
-        <v>483.7941817679998</v>
+        <v>479.8037332159998</v>
       </c>
       <c r="Q93">
-        <v>1237.294181768</v>
+        <v>1233.303733216</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4603912229296567</v>
+        <v>0.5107829401485889</v>
       </c>
       <c r="T93">
-        <v>8.524431908256577</v>
+        <v>9.560538652479169</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.332286210582406</v>
+        <v>2.306935273510859</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09386199521188709</v>
+        <v>0.0938655003601051</v>
       </c>
       <c r="C94">
-        <v>-563.713653123511</v>
+        <v>-633.37811740704</v>
       </c>
       <c r="D94">
-        <v>5422.934346876488</v>
+        <v>5422.538882592959</v>
       </c>
       <c r="E94">
-        <v>2699.447999999999</v>
+        <v>2768.717</v>
       </c>
       <c r="F94">
-        <v>6372.748</v>
+        <v>6442.017</v>
       </c>
       <c r="G94">
         <v>386.1</v>
@@ -9001,28 +9001,28 @@
         <v>1114.375</v>
       </c>
       <c r="M94">
-        <v>483.0542984</v>
+        <v>488.3048886</v>
       </c>
       <c r="N94">
-        <v>631.3207015999998</v>
+        <v>626.0701113999997</v>
       </c>
       <c r="O94">
-        <v>151.5169683839999</v>
+        <v>150.2568267359999</v>
       </c>
       <c r="P94">
-        <v>479.8037332159998</v>
+        <v>475.8132846639998</v>
       </c>
       <c r="Q94">
-        <v>1233.303733216</v>
+        <v>1229.313284664</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5107829401485889</v>
+        <v>0.5755722908586446</v>
       </c>
       <c r="T94">
-        <v>9.560538652479169</v>
+        <v>10.89267589505107</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.306935273510859</v>
+        <v>2.282129517881709</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0938655003601051</v>
+        <v>0.09386900550832311</v>
       </c>
       <c r="C95">
-        <v>-633.37811740704</v>
+        <v>-703.0425240167751</v>
       </c>
       <c r="D95">
-        <v>5422.538882592959</v>
+        <v>5422.143475983225</v>
       </c>
       <c r="E95">
-        <v>2768.717</v>
+        <v>2837.986</v>
       </c>
       <c r="F95">
-        <v>6442.017</v>
+        <v>6511.286</v>
       </c>
       <c r="G95">
         <v>386.1</v>
@@ -9083,28 +9083,28 @@
         <v>1114.375</v>
       </c>
       <c r="M95">
-        <v>488.3048886</v>
+        <v>493.5554788000001</v>
       </c>
       <c r="N95">
-        <v>626.0701113999997</v>
+        <v>620.8195211999997</v>
       </c>
       <c r="O95">
-        <v>150.2568267359999</v>
+        <v>148.9966850879999</v>
       </c>
       <c r="P95">
-        <v>475.8132846639998</v>
+        <v>471.8228361119998</v>
       </c>
       <c r="Q95">
-        <v>1229.313284664</v>
+        <v>1225.322836112</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5755722908586446</v>
+        <v>0.6619580918053857</v>
       </c>
       <c r="T95">
-        <v>10.89267589505107</v>
+        <v>12.66885888514694</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.282129517881709</v>
+        <v>2.257851544287223</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09386900550832311</v>
+        <v>0.09387251065654112</v>
       </c>
       <c r="C96">
-        <v>-703.0425240167751</v>
+        <v>-772.7068729653338</v>
       </c>
       <c r="D96">
-        <v>5422.143475983225</v>
+        <v>5421.748127034666</v>
       </c>
       <c r="E96">
-        <v>2837.986</v>
+        <v>2907.255</v>
       </c>
       <c r="F96">
-        <v>6511.286</v>
+        <v>6580.555</v>
       </c>
       <c r="G96">
         <v>386.1</v>
@@ -9165,28 +9165,28 @@
         <v>1114.375</v>
       </c>
       <c r="M96">
-        <v>493.5554788000001</v>
+        <v>498.806069</v>
       </c>
       <c r="N96">
-        <v>620.8195211999997</v>
+        <v>615.5689309999998</v>
       </c>
       <c r="O96">
-        <v>148.9966850879999</v>
+        <v>147.7365434399999</v>
       </c>
       <c r="P96">
-        <v>471.8228361119998</v>
+        <v>467.8323875599999</v>
       </c>
       <c r="Q96">
-        <v>1225.322836112</v>
+        <v>1221.33238756</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6619580918053857</v>
+        <v>0.7828982131308233</v>
       </c>
       <c r="T96">
-        <v>12.66885888514694</v>
+        <v>15.15551507128116</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.257851544287223</v>
+        <v>2.234084685926305</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09387251065654112</v>
+        <v>0.09387601580475913</v>
       </c>
       <c r="C97">
-        <v>-772.7068729653338</v>
+        <v>-842.3711642653279</v>
       </c>
       <c r="D97">
-        <v>5421.748127034666</v>
+        <v>5421.352835734672</v>
       </c>
       <c r="E97">
-        <v>2907.255</v>
+        <v>2976.524</v>
       </c>
       <c r="F97">
-        <v>6580.555</v>
+        <v>6649.824000000001</v>
       </c>
       <c r="G97">
         <v>386.1</v>
@@ -9247,28 +9247,28 @@
         <v>1114.375</v>
       </c>
       <c r="M97">
-        <v>498.806069</v>
+        <v>504.0566592000001</v>
       </c>
       <c r="N97">
-        <v>615.5689309999998</v>
+        <v>610.3183407999998</v>
       </c>
       <c r="O97">
-        <v>147.7365434399999</v>
+        <v>146.4764017919999</v>
       </c>
       <c r="P97">
-        <v>467.8323875599999</v>
+        <v>463.8419390079998</v>
       </c>
       <c r="Q97">
-        <v>1221.33238756</v>
+        <v>1217.341939008</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7828982131308233</v>
+        <v>0.9643083951189797</v>
       </c>
       <c r="T97">
-        <v>15.15551507128116</v>
+        <v>18.88549935048249</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.234084685926305</v>
+        <v>2.210812970447906</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09387601580475913</v>
+        <v>0.09387952095297714</v>
       </c>
       <c r="C98">
-        <v>-842.371164265327</v>
+        <v>-912.0353979293632</v>
       </c>
       <c r="D98">
-        <v>5421.352835734672</v>
+        <v>5420.957602070636</v>
       </c>
       <c r="E98">
-        <v>2976.523999999999</v>
+        <v>3045.793</v>
       </c>
       <c r="F98">
-        <v>6649.824</v>
+        <v>6719.093</v>
       </c>
       <c r="G98">
         <v>386.1</v>
@@ -9329,28 +9329,28 @@
         <v>1114.375</v>
       </c>
       <c r="M98">
-        <v>504.0566592</v>
+        <v>509.3072494</v>
       </c>
       <c r="N98">
-        <v>610.3183407999998</v>
+        <v>605.0677505999997</v>
       </c>
       <c r="O98">
-        <v>146.4764017919999</v>
+        <v>145.2162601439999</v>
       </c>
       <c r="P98">
-        <v>463.8419390079998</v>
+        <v>459.8514904559998</v>
       </c>
       <c r="Q98">
-        <v>1217.341939008</v>
+        <v>1213.351490456</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9643083951189773</v>
+        <v>1.26665869843257</v>
       </c>
       <c r="T98">
-        <v>18.88549935048244</v>
+        <v>25.10213981581796</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.210812970447906</v>
+        <v>2.188021084154628</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09387952095297714</v>
+        <v>0.09388302610119514</v>
       </c>
       <c r="C99">
-        <v>-912.0353979293632</v>
+        <v>-981.6995739700478</v>
       </c>
       <c r="D99">
-        <v>5420.957602070636</v>
+        <v>5420.562426029951</v>
       </c>
       <c r="E99">
-        <v>3045.793</v>
+        <v>3115.061999999999</v>
       </c>
       <c r="F99">
-        <v>6719.093</v>
+        <v>6788.361999999999</v>
       </c>
       <c r="G99">
         <v>386.1</v>
@@ -9411,28 +9411,28 @@
         <v>1114.375</v>
       </c>
       <c r="M99">
-        <v>509.3072494</v>
+        <v>514.5578396</v>
       </c>
       <c r="N99">
-        <v>605.0677505999997</v>
+        <v>599.8171603999998</v>
       </c>
       <c r="O99">
-        <v>145.2162601439999</v>
+        <v>143.956118496</v>
       </c>
       <c r="P99">
-        <v>459.8514904559998</v>
+        <v>455.8610419039999</v>
       </c>
       <c r="Q99">
-        <v>1213.351490456</v>
+        <v>1209.361041904</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.26665869843257</v>
+        <v>1.871359305059755</v>
       </c>
       <c r="T99">
-        <v>25.10213981581796</v>
+        <v>37.535420746489</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.188021084154628</v>
+        <v>2.165694338397949</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09388302610119514</v>
+        <v>0.09388653124941315</v>
       </c>
       <c r="C100">
-        <v>-981.6995739700478</v>
+        <v>-1051.363692399981</v>
       </c>
       <c r="D100">
-        <v>5420.562426029951</v>
+        <v>5420.167307600018</v>
       </c>
       <c r="E100">
-        <v>3115.061999999999</v>
+        <v>3184.330999999999</v>
       </c>
       <c r="F100">
-        <v>6788.361999999999</v>
+        <v>6857.630999999999</v>
       </c>
       <c r="G100">
         <v>386.1</v>
@@ -9493,28 +9493,28 @@
         <v>1114.375</v>
       </c>
       <c r="M100">
-        <v>514.5578396</v>
+        <v>519.8084298</v>
       </c>
       <c r="N100">
-        <v>599.8171603999998</v>
+        <v>594.5665701999998</v>
       </c>
       <c r="O100">
-        <v>143.956118496</v>
+        <v>142.6959768479999</v>
       </c>
       <c r="P100">
-        <v>455.8610419039999</v>
+        <v>451.8705933519998</v>
       </c>
       <c r="Q100">
-        <v>1209.361041904</v>
+        <v>1205.370593352</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.871359305059755</v>
+        <v>3.685461124941311</v>
       </c>
       <c r="T100">
-        <v>37.535420746489</v>
+        <v>74.83526353850213</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.165694338397949</v>
+        <v>2.143818638010091</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09388653124941315</v>
-      </c>
-      <c r="C101">
-        <v>-1051.363692399981</v>
-      </c>
-      <c r="D101">
-        <v>5420.167307600018</v>
-      </c>
-      <c r="E101">
-        <v>3184.330999999999</v>
-      </c>
-      <c r="F101">
-        <v>6857.630999999999</v>
-      </c>
-      <c r="G101">
-        <v>386.1</v>
-      </c>
-      <c r="H101">
-        <v>3253.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1867.875</v>
-      </c>
-      <c r="K101">
-        <v>753.5</v>
-      </c>
-      <c r="L101">
-        <v>1114.375</v>
-      </c>
-      <c r="M101">
-        <v>519.8084298</v>
-      </c>
-      <c r="N101">
-        <v>594.5665701999998</v>
-      </c>
-      <c r="O101">
-        <v>142.6959768479999</v>
-      </c>
-      <c r="P101">
-        <v>451.8705933519998</v>
-      </c>
-      <c r="Q101">
-        <v>1205.370593352</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.685461124941311</v>
-      </c>
-      <c r="T101">
-        <v>74.83526353850213</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.05760800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.143818638010091</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
